--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18354" windowHeight="9162"/>
+    <workbookView windowWidth="18954" windowHeight="9162"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="57">
   <si>
     <t>id</t>
   </si>
@@ -41,6 +41,9 @@
     <t>category</t>
   </si>
   <si>
+    <t>subcategory</t>
+  </si>
+  <si>
     <t>weight</t>
   </si>
   <si>
@@ -59,49 +62,64 @@
     <t>meat</t>
   </si>
   <si>
+    <t>sausages</t>
+  </si>
+  <si>
     <t>1,1 кг</t>
   </si>
   <si>
     <t>Россия</t>
   </si>
   <si>
-    <t>sosind</t>
+    <t>sosind.jpg</t>
   </si>
   <si>
     <t>Колбаса Мортаделла</t>
   </si>
   <si>
+    <t>boiled sausages</t>
+  </si>
+  <si>
     <t>0,5 кг</t>
   </si>
   <si>
-    <t>kolmor</t>
+    <t>kolmor.jpg</t>
   </si>
   <si>
     <t>Сервелат Московский</t>
   </si>
   <si>
+    <t>semi-smoked sausages</t>
+  </si>
+  <si>
     <t>0,75 кг</t>
   </si>
   <si>
-    <t>sermos</t>
+    <t>sermos.jpg</t>
   </si>
   <si>
     <t>Ветчина Столичная</t>
   </si>
   <si>
+    <t>ham</t>
+  </si>
+  <si>
     <t>2,5 кг</t>
   </si>
   <si>
-    <t>vetsto</t>
+    <t>vetsto.jpg</t>
   </si>
   <si>
     <t>Рулет Ленинградский</t>
   </si>
   <si>
+    <t>meat rolls</t>
+  </si>
+  <si>
     <t>0,4 кг</t>
   </si>
   <si>
-    <t>rullen</t>
+    <t>rullen.jpg</t>
   </si>
   <si>
     <t>Сыр Ланселот</t>
@@ -113,13 +131,16 @@
     <t>cheese</t>
   </si>
   <si>
+    <t>semi-hard</t>
+  </si>
+  <si>
     <t>6,1 кг</t>
   </si>
   <si>
     <t>Беларусь</t>
   </si>
   <si>
-    <t>lanselot</t>
+    <t>lanselot.png</t>
   </si>
   <si>
     <t>Сыр Пиковая Дама</t>
@@ -128,13 +149,13 @@
     <t>6,5 кг</t>
   </si>
   <si>
-    <t>pikdam</t>
+    <t>pikdam.jpg</t>
   </si>
   <si>
     <t>Сыр Сарматия Гройцер</t>
   </si>
   <si>
-    <t>grojcer</t>
+    <t>grojcer.jpg</t>
   </si>
   <si>
     <t>Сыр Тильзитер</t>
@@ -143,13 +164,13 @@
     <t>4 кг</t>
   </si>
   <si>
-    <t>tilbs</t>
+    <t>tilbs.jpg</t>
   </si>
   <si>
     <t>Сыр Мраморный</t>
   </si>
   <si>
-    <t>mrambs</t>
+    <t>mrambs.jpg</t>
   </si>
   <si>
     <t>Молоко</t>
@@ -164,16 +185,19 @@
     <t>0,930 л</t>
   </si>
   <si>
-    <t>moloko</t>
+    <t>moloko.png</t>
   </si>
   <si>
     <t>Кефир</t>
   </si>
   <si>
+    <t>kefir</t>
+  </si>
+  <si>
     <t>0,930 кг</t>
   </si>
   <si>
-    <t>kefir</t>
+    <t>kefir.jpg</t>
   </si>
 </sst>
 </file>
@@ -1326,10 +1350,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9.47368421052632" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9.47368421052632" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="2" max="2" width="18.3684210526316" customWidth="1"/>
+    <col min="5" max="5" width="13.2631578947368" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1351,281 +1379,320 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
+      <c r="H3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
         <v>36</v>
       </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" t="s">
-        <v>38</v>
+      <c r="H10" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>36</v>
+      </c>
+      <c r="H11" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
   <si>
     <t>id</t>
   </si>
@@ -62,7 +62,7 @@
     <t>meat</t>
   </si>
   <si>
-    <t>sausages</t>
+    <t>сосиски</t>
   </si>
   <si>
     <t>1,1 кг</t>
@@ -77,7 +77,7 @@
     <t>Колбаса Мортаделла</t>
   </si>
   <si>
-    <t>boiled sausages</t>
+    <t>вареные колбасы</t>
   </si>
   <si>
     <t>0,5 кг</t>
@@ -89,7 +89,7 @@
     <t>Сервелат Московский</t>
   </si>
   <si>
-    <t>semi-smoked sausages</t>
+    <t>полукопченая колбасы</t>
   </si>
   <si>
     <t>0,75 кг</t>
@@ -101,7 +101,7 @@
     <t>Ветчина Столичная</t>
   </si>
   <si>
-    <t>ham</t>
+    <t>ветчины</t>
   </si>
   <si>
     <t>2,5 кг</t>
@@ -113,7 +113,7 @@
     <t>Рулет Ленинградский</t>
   </si>
   <si>
-    <t>meat rolls</t>
+    <t>мясные рулеты</t>
   </si>
   <si>
     <t>0,4 кг</t>
@@ -131,7 +131,7 @@
     <t>cheese</t>
   </si>
   <si>
-    <t>semi-hard</t>
+    <t>полутвердые</t>
   </si>
   <si>
     <t>6,1 кг</t>
@@ -182,6 +182,9 @@
     <t>milk</t>
   </si>
   <si>
+    <t>молоко</t>
+  </si>
+  <si>
     <t>0,930 л</t>
   </si>
   <si>
@@ -191,7 +194,7 @@
     <t>Кефир</t>
   </si>
   <si>
-    <t>kefir</t>
+    <t>кефир</t>
   </si>
   <si>
     <t>0,930 кг</t>
@@ -1657,16 +1660,16 @@
         <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1674,7 +1677,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
         <v>49</v>
@@ -1683,16 +1686,16 @@
         <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
   <si>
     <t>id</t>
   </si>
@@ -140,9 +140,6 @@
     <t>Беларусь</t>
   </si>
   <si>
-    <t>lanselot.png</t>
-  </si>
-  <si>
     <t>Сыр Пиковая Дама</t>
   </si>
   <si>
@@ -186,9 +183,6 @@
   </si>
   <si>
     <t>0,930 л</t>
-  </si>
-  <si>
-    <t>moloko.png</t>
   </si>
   <si>
     <t>Кефир</t>
@@ -1538,16 +1532,13 @@
       <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="H7" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
@@ -1559,13 +1550,13 @@
         <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
         <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1573,7 +1564,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
@@ -1591,7 +1582,7 @@
         <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1599,7 +1590,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
@@ -1611,13 +1602,13 @@
         <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
         <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1625,7 +1616,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
@@ -1637,13 +1628,13 @@
         <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G11" t="s">
         <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1651,25 +1642,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
         <v>48</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>49</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>50</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>51</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
-      </c>
-      <c r="H12" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1677,25 +1665,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" t="s">
         <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -71,7 +71,7 @@
     <t>Россия</t>
   </si>
   <si>
-    <t>sosind.jpg</t>
+    <t>sosind.webp</t>
   </si>
   <si>
     <t>Колбаса Мортаделла</t>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="57">
   <si>
     <t>id</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Петродворские колбасы</t>
   </si>
   <si>
-    <t>meat</t>
+    <t>Колбасы</t>
   </si>
   <si>
     <t>сосиски</t>
@@ -128,7 +128,7 @@
     <t>Беловежские сыры</t>
   </si>
   <si>
-    <t>cheese</t>
+    <t>Сыры</t>
   </si>
   <si>
     <t>полутвердые</t>
@@ -176,7 +176,7 @@
     <t>КМЗ</t>
   </si>
   <si>
-    <t>milk</t>
+    <t>Молчока</t>
   </si>
   <si>
     <t>молоко</t>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>Кефир</t>
+  </si>
+  <si>
+    <t>Молочка</t>
   </si>
   <si>
     <t>кефир</t>
@@ -1671,19 +1674,19 @@
         <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3466" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3466" uniqueCount="300">
   <si>
     <t>id</t>
   </si>
@@ -185,18 +185,42 @@
     <t>1,0-1,2кг в шт.</t>
   </si>
   <si>
+    <t>seroli.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-olimpiyskiy1</t>
+  </si>
+  <si>
     <t>Сервелат "Ореховый" в/к</t>
   </si>
   <si>
+    <t>serore.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-orehovyy</t>
+  </si>
+  <si>
     <t>Сервелат "Премьер" в/к</t>
   </si>
   <si>
     <t>0,6-0,7кг в шт.</t>
   </si>
   <si>
+    <t>serpre.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-premer</t>
+  </si>
+  <si>
     <t>Сервелат "Чесночный" в/к</t>
   </si>
   <si>
+    <t>serche.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-chesnochnyy</t>
+  </si>
+  <si>
     <t>Докторская Колбаса в "Целлофане" ГОСТ</t>
   </si>
   <si>
@@ -206,7 +230,13 @@
     <t>1,6-1,7кг в шт.</t>
   </si>
   <si>
+    <t>dokcel.jpg</t>
+  </si>
+  <si>
     <t>20сут</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/doctor-cellofan</t>
   </si>
   <si>
     <t>Докторская Колбаса в б/о ГОСТ</t>
@@ -909,7 +939,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -938,13 +968,6 @@
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1394,19 +1417,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1415,7 +1438,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1424,127 +1450,125 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2338,7 +2362,7 @@
         <v>27</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I7" t="s">
         <v>29</v>
@@ -2358,8 +2382,8 @@
       <c r="N7" t="s">
         <v>32</v>
       </c>
-      <c r="O7" t="s">
-        <v>29</v>
+      <c r="O7" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="P7" t="s">
         <v>29</v>
@@ -2388,7 +2412,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
@@ -2406,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
         <v>29</v>
@@ -2426,8 +2450,8 @@
       <c r="N8" t="s">
         <v>32</v>
       </c>
-      <c r="O8" t="s">
-        <v>29</v>
+      <c r="O8" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="P8" t="s">
         <v>29</v>
@@ -2456,7 +2480,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
@@ -2468,13 +2492,13 @@
         <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="I9" t="s">
         <v>29</v>
@@ -2494,8 +2518,8 @@
       <c r="N9" t="s">
         <v>32</v>
       </c>
-      <c r="O9" t="s">
-        <v>29</v>
+      <c r="O9" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="P9" t="s">
         <v>29</v>
@@ -2524,7 +2548,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -2542,7 +2566,7 @@
         <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="I10" t="s">
         <v>29</v>
@@ -2562,8 +2586,8 @@
       <c r="N10" t="s">
         <v>32</v>
       </c>
-      <c r="O10" t="s">
-        <v>29</v>
+      <c r="O10" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="P10" t="s">
         <v>29</v>
@@ -2592,7 +2616,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -2601,16 +2625,16 @@
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="I11" t="s">
         <v>29</v>
@@ -2622,7 +2646,7 @@
         <v>29</v>
       </c>
       <c r="L11" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M11" t="s">
         <v>31</v>
@@ -2630,8 +2654,8 @@
       <c r="N11" t="s">
         <v>32</v>
       </c>
-      <c r="O11" t="s">
-        <v>29</v>
+      <c r="O11" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="P11" t="s">
         <v>29</v>
@@ -2660,7 +2684,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -2669,10 +2693,10 @@
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G12" t="s">
         <v>27</v>
@@ -2690,7 +2714,7 @@
         <v>29</v>
       </c>
       <c r="L12" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M12" t="s">
         <v>31</v>
@@ -2728,7 +2752,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
@@ -2737,10 +2761,10 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
         <v>27</v>
@@ -2758,7 +2782,7 @@
         <v>29</v>
       </c>
       <c r="L13" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M13" t="s">
         <v>31</v>
@@ -2796,7 +2820,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -2805,10 +2829,10 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s">
         <v>27</v>
@@ -2826,7 +2850,7 @@
         <v>29</v>
       </c>
       <c r="L14" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M14" t="s">
         <v>31</v>
@@ -2864,7 +2888,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -2873,10 +2897,10 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s">
         <v>27</v>
@@ -2894,7 +2918,7 @@
         <v>29</v>
       </c>
       <c r="L15" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M15" t="s">
         <v>31</v>
@@ -2932,37 +2956,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" t="s">
         <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I16" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" t="s">
-        <v>29</v>
-      </c>
-      <c r="K16" t="s">
-        <v>29</v>
-      </c>
-      <c r="L16" t="s">
-        <v>59</v>
       </c>
       <c r="M16" t="s">
         <v>31</v>
@@ -3000,7 +3024,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -3009,10 +3033,10 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s">
         <v>27</v>
@@ -3030,7 +3054,7 @@
         <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M17" t="s">
         <v>31</v>
@@ -3068,7 +3092,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -3077,10 +3101,10 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G18" t="s">
         <v>27</v>
@@ -3098,7 +3122,7 @@
         <v>29</v>
       </c>
       <c r="L18" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M18" t="s">
         <v>31</v>
@@ -3136,7 +3160,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
         <v>23</v>
@@ -3145,10 +3169,10 @@
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s">
         <v>27</v>
@@ -3166,7 +3190,7 @@
         <v>29</v>
       </c>
       <c r="L19" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M19" t="s">
         <v>31</v>
@@ -3204,7 +3228,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -3213,10 +3237,10 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
@@ -3234,7 +3258,7 @@
         <v>29</v>
       </c>
       <c r="L20" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M20" t="s">
         <v>31</v>
@@ -3272,7 +3296,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
         <v>23</v>
@@ -3281,10 +3305,10 @@
         <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -3302,7 +3326,7 @@
         <v>29</v>
       </c>
       <c r="L21" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M21" t="s">
         <v>31</v>
@@ -3340,7 +3364,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
@@ -3349,7 +3373,7 @@
         <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
@@ -3370,7 +3394,7 @@
         <v>29</v>
       </c>
       <c r="L22" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M22" t="s">
         <v>31</v>
@@ -3408,7 +3432,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -3417,10 +3441,10 @@
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s">
         <v>27</v>
@@ -3438,7 +3462,7 @@
         <v>29</v>
       </c>
       <c r="L23" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M23" t="s">
         <v>31</v>
@@ -3476,7 +3500,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
@@ -3485,10 +3509,10 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s">
         <v>27</v>
@@ -3506,7 +3530,7 @@
         <v>29</v>
       </c>
       <c r="L24" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M24" t="s">
         <v>31</v>
@@ -3544,7 +3568,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -3553,10 +3577,10 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F25" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s">
         <v>27</v>
@@ -3574,7 +3598,7 @@
         <v>29</v>
       </c>
       <c r="L25" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M25" t="s">
         <v>31</v>
@@ -3612,7 +3636,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -3621,7 +3645,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F26" t="s">
         <v>40</v>
@@ -3642,7 +3666,7 @@
         <v>29</v>
       </c>
       <c r="L26" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M26" t="s">
         <v>31</v>
@@ -3680,7 +3704,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -3689,10 +3713,10 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
         <v>27</v>
@@ -3710,7 +3734,7 @@
         <v>29</v>
       </c>
       <c r="L27" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M27" t="s">
         <v>31</v>
@@ -3748,7 +3772,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -3757,10 +3781,10 @@
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -3778,7 +3802,7 @@
         <v>29</v>
       </c>
       <c r="L28" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M28" t="s">
         <v>31</v>
@@ -3816,7 +3840,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -3825,10 +3849,10 @@
         <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G29" t="s">
         <v>27</v>
@@ -3846,10 +3870,10 @@
         <v>29</v>
       </c>
       <c r="L29" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M29" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N29" t="s">
         <v>32</v>
@@ -3884,7 +3908,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
         <v>23</v>
@@ -3893,10 +3917,10 @@
         <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G30" t="s">
         <v>27</v>
@@ -3914,7 +3938,7 @@
         <v>29</v>
       </c>
       <c r="L30" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M30" t="s">
         <v>31</v>
@@ -3952,7 +3976,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -3961,7 +3985,7 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
@@ -3982,7 +4006,7 @@
         <v>29</v>
       </c>
       <c r="L31" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M31" t="s">
         <v>31</v>
@@ -4020,7 +4044,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
         <v>23</v>
@@ -4029,7 +4053,7 @@
         <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
@@ -4050,7 +4074,7 @@
         <v>29</v>
       </c>
       <c r="L32" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M32" t="s">
         <v>31</v>
@@ -4088,7 +4112,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
         <v>23</v>
@@ -4097,10 +4121,10 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
@@ -4118,7 +4142,7 @@
         <v>29</v>
       </c>
       <c r="L33" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M33" t="s">
         <v>31</v>
@@ -4156,7 +4180,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
         <v>23</v>
@@ -4165,10 +4189,10 @@
         <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F34" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G34" t="s">
         <v>27</v>
@@ -4186,7 +4210,7 @@
         <v>29</v>
       </c>
       <c r="L34" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M34" t="s">
         <v>31</v>
@@ -4224,7 +4248,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
@@ -4233,10 +4257,10 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F35" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
@@ -4292,7 +4316,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -4301,10 +4325,10 @@
         <v>24</v>
       </c>
       <c r="E36" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F36" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G36" t="s">
         <v>27</v>
@@ -4322,7 +4346,7 @@
         <v>29</v>
       </c>
       <c r="L36" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M36" t="s">
         <v>31</v>
@@ -4360,7 +4384,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
@@ -4369,10 +4393,10 @@
         <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G37" t="s">
         <v>27</v>
@@ -4390,10 +4414,10 @@
         <v>29</v>
       </c>
       <c r="L37" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="M37" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="N37" t="s">
         <v>32</v>
@@ -4428,7 +4452,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -4437,10 +4461,10 @@
         <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G38" t="s">
         <v>27</v>
@@ -4458,7 +4482,7 @@
         <v>29</v>
       </c>
       <c r="L38" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M38" t="s">
         <v>31</v>
@@ -4496,7 +4520,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C39" t="s">
         <v>23</v>
@@ -4505,7 +4529,7 @@
         <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F39" t="s">
         <v>47</v>
@@ -4526,7 +4550,7 @@
         <v>29</v>
       </c>
       <c r="L39" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M39" t="s">
         <v>31</v>
@@ -4564,7 +4588,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
         <v>23</v>
@@ -4573,10 +4597,10 @@
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F40" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G40" t="s">
         <v>27</v>
@@ -4594,7 +4618,7 @@
         <v>29</v>
       </c>
       <c r="L40" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M40" t="s">
         <v>31</v>
@@ -4632,7 +4656,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
@@ -4641,10 +4665,10 @@
         <v>24</v>
       </c>
       <c r="E41" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F41" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G41" t="s">
         <v>27</v>
@@ -4662,7 +4686,7 @@
         <v>29</v>
       </c>
       <c r="L41" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M41" t="s">
         <v>31</v>
@@ -4700,7 +4724,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
         <v>23</v>
@@ -4709,10 +4733,10 @@
         <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F42" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G42" t="s">
         <v>27</v>
@@ -4730,7 +4754,7 @@
         <v>29</v>
       </c>
       <c r="L42" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M42" t="s">
         <v>31</v>
@@ -4768,7 +4792,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
         <v>23</v>
@@ -4777,10 +4801,10 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F43" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G43" t="s">
         <v>27</v>
@@ -4798,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="L43" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M43" t="s">
         <v>31</v>
@@ -4836,7 +4860,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
         <v>23</v>
@@ -4845,10 +4869,10 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G44" t="s">
         <v>27</v>
@@ -4866,7 +4890,7 @@
         <v>29</v>
       </c>
       <c r="L44" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M44" t="s">
         <v>31</v>
@@ -4904,7 +4928,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s">
         <v>23</v>
@@ -4913,10 +4937,10 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F45" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G45" t="s">
         <v>27</v>
@@ -4934,7 +4958,7 @@
         <v>29</v>
       </c>
       <c r="L45" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M45" t="s">
         <v>31</v>
@@ -4972,7 +4996,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
         <v>23</v>
@@ -4981,10 +5005,10 @@
         <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F46" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G46" t="s">
         <v>27</v>
@@ -5002,7 +5026,7 @@
         <v>29</v>
       </c>
       <c r="L46" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M46" t="s">
         <v>31</v>
@@ -5040,7 +5064,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -5049,10 +5073,10 @@
         <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F47" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G47" t="s">
         <v>27</v>
@@ -5070,7 +5094,7 @@
         <v>29</v>
       </c>
       <c r="L47" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M47" t="s">
         <v>31</v>
@@ -5108,7 +5132,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C48" t="s">
         <v>23</v>
@@ -5117,10 +5141,10 @@
         <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F48" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G48" t="s">
         <v>27</v>
@@ -5138,7 +5162,7 @@
         <v>29</v>
       </c>
       <c r="L48" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M48" t="s">
         <v>31</v>
@@ -5176,7 +5200,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C49" t="s">
         <v>23</v>
@@ -5185,10 +5209,10 @@
         <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F49" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G49" t="s">
         <v>27</v>
@@ -5206,7 +5230,7 @@
         <v>29</v>
       </c>
       <c r="L49" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M49" t="s">
         <v>31</v>
@@ -5244,7 +5268,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C50" t="s">
         <v>23</v>
@@ -5253,7 +5277,7 @@
         <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F50" t="s">
         <v>51</v>
@@ -5274,7 +5298,7 @@
         <v>29</v>
       </c>
       <c r="L50" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M50" t="s">
         <v>31</v>
@@ -5312,7 +5336,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C51" t="s">
         <v>23</v>
@@ -5321,10 +5345,10 @@
         <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F51" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G51" t="s">
         <v>27</v>
@@ -5342,7 +5366,7 @@
         <v>29</v>
       </c>
       <c r="L51" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M51" t="s">
         <v>31</v>
@@ -5380,7 +5404,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
@@ -5389,10 +5413,10 @@
         <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F52" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
@@ -5410,7 +5434,7 @@
         <v>29</v>
       </c>
       <c r="L52" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M52" t="s">
         <v>31</v>
@@ -5448,7 +5472,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
@@ -5457,10 +5481,10 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F53" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G53" t="s">
         <v>27</v>
@@ -5478,7 +5502,7 @@
         <v>29</v>
       </c>
       <c r="L53" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M53" t="s">
         <v>31</v>
@@ -5516,7 +5540,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
@@ -5525,10 +5549,10 @@
         <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F54" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G54" t="s">
         <v>27</v>
@@ -5546,7 +5570,7 @@
         <v>29</v>
       </c>
       <c r="L54" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M54" t="s">
         <v>31</v>
@@ -5584,7 +5608,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
@@ -5593,10 +5617,10 @@
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F55" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G55" t="s">
         <v>27</v>
@@ -5614,7 +5638,7 @@
         <v>29</v>
       </c>
       <c r="L55" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M55" t="s">
         <v>31</v>
@@ -5652,7 +5676,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
@@ -5661,10 +5685,10 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F56" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G56" t="s">
         <v>27</v>
@@ -5682,7 +5706,7 @@
         <v>29</v>
       </c>
       <c r="L56" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M56" t="s">
         <v>31</v>
@@ -5720,7 +5744,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C57" t="s">
         <v>23</v>
@@ -5729,10 +5753,10 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F57" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G57" t="s">
         <v>27</v>
@@ -5750,7 +5774,7 @@
         <v>29</v>
       </c>
       <c r="L57" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M57" t="s">
         <v>31</v>
@@ -5788,7 +5812,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C58" t="s">
         <v>23</v>
@@ -5797,10 +5821,10 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F58" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G58" t="s">
         <v>27</v>
@@ -5818,7 +5842,7 @@
         <v>29</v>
       </c>
       <c r="L58" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M58" t="s">
         <v>31</v>
@@ -5856,7 +5880,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C59" t="s">
         <v>23</v>
@@ -5865,10 +5889,10 @@
         <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F59" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G59" t="s">
         <v>27</v>
@@ -5886,7 +5910,7 @@
         <v>29</v>
       </c>
       <c r="L59" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M59" t="s">
         <v>31</v>
@@ -5924,7 +5948,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
@@ -5933,10 +5957,10 @@
         <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F60" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -5954,7 +5978,7 @@
         <v>29</v>
       </c>
       <c r="L60" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M60" t="s">
         <v>31</v>
@@ -5992,7 +6016,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -6001,10 +6025,10 @@
         <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F61" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -6022,7 +6046,7 @@
         <v>29</v>
       </c>
       <c r="L61" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M61" t="s">
         <v>31</v>
@@ -6060,7 +6084,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C62" t="s">
         <v>23</v>
@@ -6069,10 +6093,10 @@
         <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F62" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -6090,7 +6114,7 @@
         <v>29</v>
       </c>
       <c r="L62" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M62" t="s">
         <v>31</v>
@@ -6128,7 +6152,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C63" t="s">
         <v>23</v>
@@ -6137,7 +6161,7 @@
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F63" t="s">
         <v>47</v>
@@ -6158,7 +6182,7 @@
         <v>29</v>
       </c>
       <c r="L63" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M63" t="s">
         <v>31</v>
@@ -6196,7 +6220,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
@@ -6205,10 +6229,10 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F64" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G64" t="s">
         <v>27</v>
@@ -6226,7 +6250,7 @@
         <v>29</v>
       </c>
       <c r="L64" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M64" t="s">
         <v>31</v>
@@ -6264,7 +6288,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C65" t="s">
         <v>23</v>
@@ -6273,10 +6297,10 @@
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F65" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G65" t="s">
         <v>27</v>
@@ -6294,7 +6318,7 @@
         <v>29</v>
       </c>
       <c r="L65" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M65" t="s">
         <v>31</v>
@@ -6332,7 +6356,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C66" t="s">
         <v>23</v>
@@ -6341,10 +6365,10 @@
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F66" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -6362,7 +6386,7 @@
         <v>29</v>
       </c>
       <c r="L66" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M66" t="s">
         <v>31</v>
@@ -6400,7 +6424,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C67" t="s">
         <v>23</v>
@@ -6409,10 +6433,10 @@
         <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F67" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G67" t="s">
         <v>27</v>
@@ -6430,7 +6454,7 @@
         <v>29</v>
       </c>
       <c r="L67" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M67" t="s">
         <v>31</v>
@@ -6468,7 +6492,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C68" t="s">
         <v>23</v>
@@ -6477,10 +6501,10 @@
         <v>24</v>
       </c>
       <c r="E68" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F68" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G68" t="s">
         <v>27</v>
@@ -6498,7 +6522,7 @@
         <v>29</v>
       </c>
       <c r="L68" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M68" t="s">
         <v>31</v>
@@ -6536,7 +6560,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
@@ -6545,10 +6569,10 @@
         <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F69" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G69" t="s">
         <v>27</v>
@@ -6566,7 +6590,7 @@
         <v>29</v>
       </c>
       <c r="L69" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M69" t="s">
         <v>31</v>
@@ -6604,7 +6628,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
@@ -6613,10 +6637,10 @@
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F70" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G70" t="s">
         <v>27</v>
@@ -6634,10 +6658,10 @@
         <v>29</v>
       </c>
       <c r="L70" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M70" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="N70" t="s">
         <v>32</v>
@@ -6672,7 +6696,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
@@ -6681,7 +6705,7 @@
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F71" t="s">
         <v>47</v>
@@ -6702,10 +6726,10 @@
         <v>29</v>
       </c>
       <c r="L71" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M71" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="N71" t="s">
         <v>32</v>
@@ -6740,7 +6764,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C72" t="s">
         <v>23</v>
@@ -6749,7 +6773,7 @@
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F72" t="s">
         <v>40</v>
@@ -6770,10 +6794,10 @@
         <v>29</v>
       </c>
       <c r="L72" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M72" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="N72" t="s">
         <v>32</v>
@@ -6808,7 +6832,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C73" t="s">
         <v>23</v>
@@ -6817,10 +6841,10 @@
         <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F73" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G73" t="s">
         <v>27</v>
@@ -6838,7 +6862,7 @@
         <v>29</v>
       </c>
       <c r="L73" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M73" t="s">
         <v>31</v>
@@ -6876,7 +6900,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C74" t="s">
         <v>23</v>
@@ -6885,10 +6909,10 @@
         <v>24</v>
       </c>
       <c r="E74" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F74" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G74" t="s">
         <v>27</v>
@@ -6906,7 +6930,7 @@
         <v>29</v>
       </c>
       <c r="L74" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="M74" t="s">
         <v>31</v>
@@ -6944,7 +6968,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C75" t="s">
         <v>23</v>
@@ -6953,10 +6977,10 @@
         <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F75" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="G75" t="s">
         <v>27</v>
@@ -7012,7 +7036,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -7021,10 +7045,10 @@
         <v>24</v>
       </c>
       <c r="E76" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F76" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G76" t="s">
         <v>27</v>
@@ -7042,7 +7066,7 @@
         <v>29</v>
       </c>
       <c r="L76" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="M76" t="s">
         <v>31</v>
@@ -7080,7 +7104,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C77" t="s">
         <v>23</v>
@@ -7089,10 +7113,10 @@
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F77" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G77" t="s">
         <v>27</v>
@@ -7110,7 +7134,7 @@
         <v>29</v>
       </c>
       <c r="L77" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M77" t="s">
         <v>31</v>
@@ -7148,7 +7172,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C78" t="s">
         <v>23</v>
@@ -7157,10 +7181,10 @@
         <v>24</v>
       </c>
       <c r="E78" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F78" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G78" t="s">
         <v>27</v>
@@ -7178,7 +7202,7 @@
         <v>29</v>
       </c>
       <c r="L78" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="M78" t="s">
         <v>31</v>
@@ -7216,7 +7240,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C79" t="s">
         <v>23</v>
@@ -7225,10 +7249,10 @@
         <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F79" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="G79" t="s">
         <v>27</v>
@@ -7284,7 +7308,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C80" t="s">
         <v>23</v>
@@ -7293,7 +7317,7 @@
         <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F80" t="s">
         <v>40</v>
@@ -7317,7 +7341,7 @@
         <v>30</v>
       </c>
       <c r="M80" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="N80" t="s">
         <v>32</v>
@@ -7352,7 +7376,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C81" t="s">
         <v>23</v>
@@ -7361,7 +7385,7 @@
         <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F81" t="s">
         <v>40</v>
@@ -7385,7 +7409,7 @@
         <v>30</v>
       </c>
       <c r="M81" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="N81" t="s">
         <v>32</v>
@@ -7420,7 +7444,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
@@ -7429,10 +7453,10 @@
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F82" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G82" t="s">
         <v>27</v>
@@ -7453,7 +7477,7 @@
         <v>30</v>
       </c>
       <c r="M82" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="N82" t="s">
         <v>32</v>
@@ -7488,7 +7512,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
@@ -7497,10 +7521,10 @@
         <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F83" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G83" t="s">
         <v>27</v>
@@ -7521,7 +7545,7 @@
         <v>30</v>
       </c>
       <c r="M83" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="N83" t="s">
         <v>32</v>
@@ -7556,7 +7580,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C84" t="s">
         <v>23</v>
@@ -7565,10 +7589,10 @@
         <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F84" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G84" t="s">
         <v>27</v>
@@ -7586,10 +7610,10 @@
         <v>29</v>
       </c>
       <c r="L84" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="M84" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="N84" t="s">
         <v>32</v>
@@ -7624,7 +7648,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
@@ -7633,10 +7657,10 @@
         <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F85" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G85" t="s">
         <v>27</v>
@@ -7654,10 +7678,10 @@
         <v>29</v>
       </c>
       <c r="L85" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="M85" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="N85" t="s">
         <v>32</v>
@@ -7692,7 +7716,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C86" t="s">
         <v>23</v>
@@ -7701,10 +7725,10 @@
         <v>24</v>
       </c>
       <c r="E86" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F86" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G86" t="s">
         <v>27</v>
@@ -7722,10 +7746,10 @@
         <v>29</v>
       </c>
       <c r="L86" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="M86" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="N86" t="s">
         <v>32</v>
@@ -7760,7 +7784,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
@@ -7769,7 +7793,7 @@
         <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F87" t="s">
         <v>40</v>
@@ -7793,7 +7817,7 @@
         <v>30</v>
       </c>
       <c r="M87" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="N87" t="s">
         <v>32</v>
@@ -7828,7 +7852,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C88" t="s">
         <v>23</v>
@@ -7837,10 +7861,10 @@
         <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F88" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G88" t="s">
         <v>27</v>
@@ -7858,7 +7882,7 @@
         <v>29</v>
       </c>
       <c r="L88" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M88" t="s">
         <v>31</v>
@@ -7896,7 +7920,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="C89" t="s">
         <v>23</v>
@@ -7905,10 +7929,10 @@
         <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F89" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G89" t="s">
         <v>27</v>
@@ -7964,7 +7988,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C90" t="s">
         <v>23</v>
@@ -7973,10 +7997,10 @@
         <v>24</v>
       </c>
       <c r="E90" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F90" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G90" t="s">
         <v>27</v>
@@ -7997,7 +8021,7 @@
         <v>30</v>
       </c>
       <c r="M90" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N90" t="s">
         <v>32</v>
@@ -8032,7 +8056,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C91" t="s">
         <v>23</v>
@@ -8041,7 +8065,7 @@
         <v>24</v>
       </c>
       <c r="E91" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F91" t="s">
         <v>26</v>
@@ -8100,7 +8124,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C92" t="s">
         <v>23</v>
@@ -8109,10 +8133,10 @@
         <v>24</v>
       </c>
       <c r="E92" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F92" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G92" t="s">
         <v>27</v>
@@ -8133,7 +8157,7 @@
         <v>30</v>
       </c>
       <c r="M92" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N92" t="s">
         <v>32</v>
@@ -8168,7 +8192,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C93" t="s">
         <v>23</v>
@@ -8177,10 +8201,10 @@
         <v>24</v>
       </c>
       <c r="E93" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F93" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G93" t="s">
         <v>27</v>
@@ -8198,10 +8222,10 @@
         <v>29</v>
       </c>
       <c r="L93" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="M93" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="N93" t="s">
         <v>32</v>
@@ -8236,7 +8260,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C94" t="s">
         <v>23</v>
@@ -8245,10 +8269,10 @@
         <v>24</v>
       </c>
       <c r="E94" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F94" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G94" t="s">
         <v>27</v>
@@ -8304,7 +8328,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C95" t="s">
         <v>23</v>
@@ -8313,10 +8337,10 @@
         <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F95" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="G95" t="s">
         <v>27</v>
@@ -8334,10 +8358,10 @@
         <v>29</v>
       </c>
       <c r="L95" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M95" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N95" t="s">
         <v>32</v>
@@ -8372,7 +8396,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C96" t="s">
         <v>23</v>
@@ -8381,10 +8405,10 @@
         <v>24</v>
       </c>
       <c r="E96" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F96" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="G96" t="s">
         <v>27</v>
@@ -8405,7 +8429,7 @@
         <v>30</v>
       </c>
       <c r="M96" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N96" t="s">
         <v>32</v>
@@ -8440,7 +8464,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C97" t="s">
         <v>23</v>
@@ -8449,10 +8473,10 @@
         <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F97" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G97" t="s">
         <v>27</v>
@@ -8473,7 +8497,7 @@
         <v>30</v>
       </c>
       <c r="M97" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N97" t="s">
         <v>32</v>
@@ -8508,7 +8532,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C98" t="s">
         <v>23</v>
@@ -8517,10 +8541,10 @@
         <v>24</v>
       </c>
       <c r="E98" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F98" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="G98" t="s">
         <v>27</v>
@@ -8541,7 +8565,7 @@
         <v>30</v>
       </c>
       <c r="M98" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N98" t="s">
         <v>32</v>
@@ -8576,7 +8600,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
@@ -8585,10 +8609,10 @@
         <v>24</v>
       </c>
       <c r="E99" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F99" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G99" t="s">
         <v>27</v>
@@ -8644,7 +8668,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
@@ -8653,10 +8677,10 @@
         <v>24</v>
       </c>
       <c r="E100" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F100" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G100" t="s">
         <v>27</v>
@@ -8677,7 +8701,7 @@
         <v>30</v>
       </c>
       <c r="M100" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N100" t="s">
         <v>32</v>
@@ -8712,7 +8736,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C101" t="s">
         <v>23</v>
@@ -8721,10 +8745,10 @@
         <v>24</v>
       </c>
       <c r="E101" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F101" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G101" t="s">
         <v>27</v>
@@ -8745,7 +8769,7 @@
         <v>30</v>
       </c>
       <c r="M101" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N101" t="s">
         <v>32</v>
@@ -8780,7 +8804,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
@@ -8789,10 +8813,10 @@
         <v>24</v>
       </c>
       <c r="E102" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F102" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G102" t="s">
         <v>27</v>
@@ -8813,7 +8837,7 @@
         <v>30</v>
       </c>
       <c r="M102" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N102" t="s">
         <v>32</v>
@@ -8848,7 +8872,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
@@ -8857,10 +8881,10 @@
         <v>24</v>
       </c>
       <c r="E103" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F103" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G103" t="s">
         <v>27</v>
@@ -8881,7 +8905,7 @@
         <v>30</v>
       </c>
       <c r="M103" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N103" t="s">
         <v>32</v>
@@ -8916,7 +8940,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C104" t="s">
         <v>23</v>
@@ -8925,7 +8949,7 @@
         <v>24</v>
       </c>
       <c r="E104" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F104" t="s">
         <v>26</v>
@@ -8984,7 +9008,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
@@ -8993,7 +9017,7 @@
         <v>24</v>
       </c>
       <c r="E105" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F105" t="s">
         <v>40</v>
@@ -9017,7 +9041,7 @@
         <v>30</v>
       </c>
       <c r="M105" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N105" t="s">
         <v>32</v>
@@ -9052,7 +9076,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C106" t="s">
         <v>23</v>
@@ -9061,10 +9085,10 @@
         <v>24</v>
       </c>
       <c r="E106" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F106" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G106" t="s">
         <v>27</v>
@@ -9120,7 +9144,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C107" t="s">
         <v>23</v>
@@ -9129,10 +9153,10 @@
         <v>24</v>
       </c>
       <c r="E107" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F107" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G107" t="s">
         <v>27</v>
@@ -9153,7 +9177,7 @@
         <v>30</v>
       </c>
       <c r="M107" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N107" t="s">
         <v>32</v>
@@ -9188,7 +9212,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C108" t="s">
         <v>23</v>
@@ -9197,10 +9221,10 @@
         <v>24</v>
       </c>
       <c r="E108" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F108" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G108" t="s">
         <v>27</v>
@@ -9221,7 +9245,7 @@
         <v>30</v>
       </c>
       <c r="M108" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="N108" t="s">
         <v>32</v>
@@ -9256,7 +9280,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C109" t="s">
         <v>23</v>
@@ -9265,10 +9289,10 @@
         <v>24</v>
       </c>
       <c r="E109" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F109" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="G109" t="s">
         <v>27</v>
@@ -9286,7 +9310,7 @@
         <v>29</v>
       </c>
       <c r="L109" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="M109" t="s">
         <v>31</v>
@@ -9324,7 +9348,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C110" t="s">
         <v>23</v>
@@ -9333,10 +9357,10 @@
         <v>24</v>
       </c>
       <c r="E110" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F110" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G110" t="s">
         <v>27</v>
@@ -9354,7 +9378,7 @@
         <v>29</v>
       </c>
       <c r="L110" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="M110" t="s">
         <v>31</v>
@@ -9392,7 +9416,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C111" t="s">
         <v>23</v>
@@ -9401,10 +9425,10 @@
         <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F111" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="G111" t="s">
         <v>27</v>
@@ -9422,7 +9446,7 @@
         <v>29</v>
       </c>
       <c r="L111" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="M111" t="s">
         <v>31</v>
@@ -9460,7 +9484,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C112" t="s">
         <v>23</v>
@@ -9469,10 +9493,10 @@
         <v>24</v>
       </c>
       <c r="E112" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F112" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="G112" t="s">
         <v>27</v>
@@ -9490,10 +9514,10 @@
         <v>29</v>
       </c>
       <c r="L112" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="M112" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="N112" t="s">
         <v>32</v>
@@ -9528,7 +9552,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C113" t="s">
         <v>23</v>
@@ -9537,10 +9561,10 @@
         <v>24</v>
       </c>
       <c r="E113" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F113" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -9596,7 +9620,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C114" t="s">
         <v>23</v>
@@ -9605,10 +9629,10 @@
         <v>24</v>
       </c>
       <c r="E114" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F114" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -9664,7 +9688,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
@@ -9673,10 +9697,10 @@
         <v>24</v>
       </c>
       <c r="E115" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F115" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G115" t="s">
         <v>27</v>
@@ -9694,7 +9718,7 @@
         <v>29</v>
       </c>
       <c r="L115" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M115" t="s">
         <v>31</v>
@@ -9732,7 +9756,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
@@ -9741,10 +9765,10 @@
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F116" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G116" t="s">
         <v>27</v>
@@ -9762,7 +9786,7 @@
         <v>29</v>
       </c>
       <c r="L116" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M116" t="s">
         <v>31</v>
@@ -9800,7 +9824,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C117" t="s">
         <v>23</v>
@@ -9809,10 +9833,10 @@
         <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F117" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G117" t="s">
         <v>27</v>
@@ -9830,7 +9854,7 @@
         <v>29</v>
       </c>
       <c r="L117" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M117" t="s">
         <v>31</v>
@@ -9868,7 +9892,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C118" t="s">
         <v>23</v>
@@ -9877,10 +9901,10 @@
         <v>24</v>
       </c>
       <c r="E118" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F118" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G118" t="s">
         <v>27</v>
@@ -9898,7 +9922,7 @@
         <v>29</v>
       </c>
       <c r="L118" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M118" t="s">
         <v>31</v>
@@ -9936,7 +9960,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -9945,10 +9969,10 @@
         <v>24</v>
       </c>
       <c r="E119" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F119" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G119" t="s">
         <v>27</v>
@@ -9966,10 +9990,10 @@
         <v>29</v>
       </c>
       <c r="L119" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M119" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N119" t="s">
         <v>32</v>
@@ -10004,7 +10028,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C120" t="s">
         <v>23</v>
@@ -10013,10 +10037,10 @@
         <v>24</v>
       </c>
       <c r="E120" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F120" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G120" t="s">
         <v>27</v>
@@ -10034,10 +10058,10 @@
         <v>29</v>
       </c>
       <c r="L120" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M120" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N120" t="s">
         <v>32</v>
@@ -10072,7 +10096,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C121" t="s">
         <v>23</v>
@@ -10081,10 +10105,10 @@
         <v>24</v>
       </c>
       <c r="E121" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F121" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G121" t="s">
         <v>27</v>
@@ -10102,10 +10126,10 @@
         <v>29</v>
       </c>
       <c r="L121" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M121" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N121" t="s">
         <v>32</v>
@@ -10140,7 +10164,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C122" t="s">
         <v>23</v>
@@ -10149,10 +10173,10 @@
         <v>24</v>
       </c>
       <c r="E122" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F122" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -10170,10 +10194,10 @@
         <v>29</v>
       </c>
       <c r="L122" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M122" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N122" t="s">
         <v>32</v>
@@ -10208,7 +10232,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C123" t="s">
         <v>23</v>
@@ -10217,10 +10241,10 @@
         <v>24</v>
       </c>
       <c r="E123" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F123" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -10238,10 +10262,10 @@
         <v>29</v>
       </c>
       <c r="L123" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M123" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N123" t="s">
         <v>32</v>
@@ -10276,7 +10300,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C124" t="s">
         <v>23</v>
@@ -10285,10 +10309,10 @@
         <v>24</v>
       </c>
       <c r="E124" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F124" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G124" t="s">
         <v>27</v>
@@ -10306,10 +10330,10 @@
         <v>29</v>
       </c>
       <c r="L124" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M124" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N124" t="s">
         <v>32</v>
@@ -10344,7 +10368,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C125" t="s">
         <v>23</v>
@@ -10353,10 +10377,10 @@
         <v>24</v>
       </c>
       <c r="E125" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F125" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G125" t="s">
         <v>27</v>
@@ -10374,10 +10398,10 @@
         <v>29</v>
       </c>
       <c r="L125" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M125" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N125" t="s">
         <v>32</v>
@@ -10412,7 +10436,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
@@ -10421,10 +10445,10 @@
         <v>24</v>
       </c>
       <c r="E126" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F126" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G126" t="s">
         <v>27</v>
@@ -10442,10 +10466,10 @@
         <v>29</v>
       </c>
       <c r="L126" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M126" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N126" t="s">
         <v>32</v>
@@ -10480,7 +10504,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C127" t="s">
         <v>23</v>
@@ -10489,10 +10513,10 @@
         <v>24</v>
       </c>
       <c r="E127" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F127" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G127" t="s">
         <v>27</v>
@@ -10510,10 +10534,10 @@
         <v>29</v>
       </c>
       <c r="L127" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M127" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N127" t="s">
         <v>32</v>
@@ -10548,7 +10572,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
@@ -10557,10 +10581,10 @@
         <v>24</v>
       </c>
       <c r="E128" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F128" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G128" t="s">
         <v>27</v>
@@ -10578,10 +10602,10 @@
         <v>29</v>
       </c>
       <c r="L128" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M128" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N128" t="s">
         <v>32</v>
@@ -10616,7 +10640,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
@@ -10625,10 +10649,10 @@
         <v>24</v>
       </c>
       <c r="E129" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F129" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
@@ -10646,7 +10670,7 @@
         <v>29</v>
       </c>
       <c r="L129" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="M129" t="s">
         <v>31</v>
@@ -10684,7 +10708,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
@@ -10693,10 +10717,10 @@
         <v>24</v>
       </c>
       <c r="E130" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F130" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G130" t="s">
         <v>27</v>
@@ -10714,7 +10738,7 @@
         <v>29</v>
       </c>
       <c r="L130" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="M130" t="s">
         <v>31</v>
@@ -10752,7 +10776,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C131" t="s">
         <v>23</v>
@@ -10761,10 +10785,10 @@
         <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F131" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="G131" t="s">
         <v>27</v>
@@ -10782,7 +10806,7 @@
         <v>29</v>
       </c>
       <c r="L131" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M131" t="s">
         <v>31</v>
@@ -10820,7 +10844,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C132" t="s">
         <v>23</v>
@@ -10829,10 +10853,10 @@
         <v>24</v>
       </c>
       <c r="E132" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F132" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -10850,7 +10874,7 @@
         <v>29</v>
       </c>
       <c r="L132" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M132" t="s">
         <v>31</v>
@@ -10888,7 +10912,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -10897,10 +10921,10 @@
         <v>24</v>
       </c>
       <c r="E133" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F133" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G133" t="s">
         <v>27</v>
@@ -10918,7 +10942,7 @@
         <v>29</v>
       </c>
       <c r="L133" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="M133" t="s">
         <v>31</v>
@@ -10956,7 +10980,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C134" t="s">
         <v>23</v>
@@ -10965,10 +10989,10 @@
         <v>24</v>
       </c>
       <c r="E134" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F134" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G134" t="s">
         <v>27</v>
@@ -10986,7 +11010,7 @@
         <v>29</v>
       </c>
       <c r="L134" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M134" t="s">
         <v>31</v>
@@ -11024,19 +11048,19 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
+        <v>260</v>
+      </c>
+      <c r="C135" t="s">
+        <v>23</v>
+      </c>
+      <c r="D135" t="s">
+        <v>24</v>
+      </c>
+      <c r="E135" t="s">
         <v>250</v>
       </c>
-      <c r="C135" t="s">
-        <v>23</v>
-      </c>
-      <c r="D135" t="s">
-        <v>24</v>
-      </c>
-      <c r="E135" t="s">
-        <v>240</v>
-      </c>
       <c r="F135" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G135" t="s">
         <v>27</v>
@@ -11054,7 +11078,7 @@
         <v>29</v>
       </c>
       <c r="L135" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="M135" t="s">
         <v>31</v>
@@ -11092,7 +11116,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="C136" t="s">
         <v>23</v>
@@ -11101,10 +11125,10 @@
         <v>24</v>
       </c>
       <c r="E136" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F136" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="G136" t="s">
         <v>27</v>
@@ -11122,10 +11146,10 @@
         <v>29</v>
       </c>
       <c r="L136" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M136" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="N136" t="s">
         <v>32</v>
@@ -11160,7 +11184,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C137" t="s">
         <v>23</v>
@@ -11169,10 +11193,10 @@
         <v>24</v>
       </c>
       <c r="E137" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F137" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G137" t="s">
         <v>27</v>
@@ -11190,7 +11214,7 @@
         <v>29</v>
       </c>
       <c r="L137" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="M137" t="s">
         <v>31</v>
@@ -11228,7 +11252,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C138" t="s">
         <v>23</v>
@@ -11237,10 +11261,10 @@
         <v>24</v>
       </c>
       <c r="E138" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F138" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G138" t="s">
         <v>27</v>
@@ -11258,7 +11282,7 @@
         <v>29</v>
       </c>
       <c r="L138" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="M138" t="s">
         <v>31</v>
@@ -11296,7 +11320,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C139" t="s">
         <v>23</v>
@@ -11305,10 +11329,10 @@
         <v>24</v>
       </c>
       <c r="E139" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F139" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G139" t="s">
         <v>27</v>
@@ -11326,7 +11350,7 @@
         <v>29</v>
       </c>
       <c r="L139" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M139" t="s">
         <v>31</v>
@@ -11364,7 +11388,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="C140" t="s">
         <v>23</v>
@@ -11373,10 +11397,10 @@
         <v>24</v>
       </c>
       <c r="E140" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F140" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="G140" t="s">
         <v>27</v>
@@ -11394,7 +11418,7 @@
         <v>29</v>
       </c>
       <c r="L140" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M140" t="s">
         <v>31</v>
@@ -11432,7 +11456,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C141" t="s">
         <v>23</v>
@@ -11441,10 +11465,10 @@
         <v>24</v>
       </c>
       <c r="E141" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F141" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="G141" t="s">
         <v>27</v>
@@ -11462,7 +11486,7 @@
         <v>29</v>
       </c>
       <c r="L141" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M141" t="s">
         <v>31</v>
@@ -11500,7 +11524,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C142" t="s">
         <v>23</v>
@@ -11509,10 +11533,10 @@
         <v>24</v>
       </c>
       <c r="E142" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F142" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G142" t="s">
         <v>27</v>
@@ -11530,7 +11554,7 @@
         <v>29</v>
       </c>
       <c r="L142" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M142" t="s">
         <v>31</v>
@@ -11568,7 +11592,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="C143" t="s">
         <v>23</v>
@@ -11577,10 +11601,10 @@
         <v>24</v>
       </c>
       <c r="E143" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F143" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G143" t="s">
         <v>27</v>
@@ -11636,7 +11660,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C144" t="s">
         <v>23</v>
@@ -11645,10 +11669,10 @@
         <v>24</v>
       </c>
       <c r="E144" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F144" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="G144" t="s">
         <v>27</v>
@@ -11666,7 +11690,7 @@
         <v>29</v>
       </c>
       <c r="L144" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M144" t="s">
         <v>31</v>
@@ -11704,7 +11728,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C145" t="s">
         <v>23</v>
@@ -11713,10 +11737,10 @@
         <v>24</v>
       </c>
       <c r="E145" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F145" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="G145" t="s">
         <v>27</v>
@@ -11734,7 +11758,7 @@
         <v>29</v>
       </c>
       <c r="L145" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M145" t="s">
         <v>31</v>
@@ -11772,7 +11796,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="C146" t="s">
         <v>23</v>
@@ -11781,10 +11805,10 @@
         <v>24</v>
       </c>
       <c r="E146" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F146" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="G146" t="s">
         <v>27</v>
@@ -11802,7 +11826,7 @@
         <v>29</v>
       </c>
       <c r="L146" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M146" t="s">
         <v>31</v>
@@ -11840,7 +11864,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="C147" t="s">
         <v>23</v>
@@ -11849,10 +11873,10 @@
         <v>24</v>
       </c>
       <c r="E147" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F147" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="G147" t="s">
         <v>27</v>
@@ -11870,7 +11894,7 @@
         <v>29</v>
       </c>
       <c r="L147" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M147" t="s">
         <v>31</v>
@@ -11908,7 +11932,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C148" t="s">
         <v>23</v>
@@ -11917,10 +11941,10 @@
         <v>24</v>
       </c>
       <c r="E148" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F148" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G148" t="s">
         <v>27</v>
@@ -11938,7 +11962,7 @@
         <v>29</v>
       </c>
       <c r="L148" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M148" t="s">
         <v>31</v>
@@ -11976,7 +12000,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C149" t="s">
         <v>23</v>
@@ -11985,10 +12009,10 @@
         <v>24</v>
       </c>
       <c r="E149" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F149" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G149" t="s">
         <v>27</v>
@@ -12006,7 +12030,7 @@
         <v>29</v>
       </c>
       <c r="L149" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M149" t="s">
         <v>31</v>
@@ -12044,7 +12068,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C150" t="s">
         <v>23</v>
@@ -12053,10 +12077,10 @@
         <v>24</v>
       </c>
       <c r="E150" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F150" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G150" t="s">
         <v>27</v>
@@ -12074,7 +12098,7 @@
         <v>29</v>
       </c>
       <c r="L150" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M150" t="s">
         <v>31</v>
@@ -12112,7 +12136,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C151" t="s">
         <v>23</v>
@@ -12121,10 +12145,10 @@
         <v>24</v>
       </c>
       <c r="E151" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F151" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="G151" t="s">
         <v>27</v>
@@ -12142,7 +12166,7 @@
         <v>29</v>
       </c>
       <c r="L151" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M151" t="s">
         <v>31</v>
@@ -12180,7 +12204,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C152" t="s">
         <v>23</v>
@@ -12189,10 +12213,10 @@
         <v>24</v>
       </c>
       <c r="E152" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F152" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="G152" t="s">
         <v>27</v>
@@ -12210,7 +12234,7 @@
         <v>29</v>
       </c>
       <c r="L152" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M152" t="s">
         <v>31</v>
@@ -12248,7 +12272,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C153" t="s">
         <v>23</v>
@@ -12257,10 +12281,10 @@
         <v>24</v>
       </c>
       <c r="E153" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F153" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="G153" t="s">
         <v>27</v>
@@ -12278,7 +12302,7 @@
         <v>29</v>
       </c>
       <c r="L153" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M153" t="s">
         <v>31</v>
@@ -12316,7 +12340,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="C154" t="s">
         <v>23</v>
@@ -12325,10 +12349,10 @@
         <v>24</v>
       </c>
       <c r="E154" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F154" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="G154" t="s">
         <v>27</v>
@@ -12346,7 +12370,7 @@
         <v>29</v>
       </c>
       <c r="L154" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M154" t="s">
         <v>31</v>
@@ -12384,7 +12408,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="C155" t="s">
         <v>23</v>
@@ -12393,10 +12417,10 @@
         <v>24</v>
       </c>
       <c r="E155" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F155" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="G155" t="s">
         <v>27</v>
@@ -12414,7 +12438,7 @@
         <v>29</v>
       </c>
       <c r="L155" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M155" t="s">
         <v>31</v>
@@ -12452,7 +12476,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="C156" t="s">
         <v>23</v>
@@ -12461,10 +12485,10 @@
         <v>24</v>
       </c>
       <c r="E156" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F156" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="G156" t="s">
         <v>27</v>
@@ -12482,7 +12506,7 @@
         <v>29</v>
       </c>
       <c r="L156" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M156" t="s">
         <v>31</v>
@@ -12520,20 +12544,20 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>291</v>
+      </c>
+      <c r="C157" t="s">
+        <v>23</v>
+      </c>
+      <c r="D157" t="s">
+        <v>24</v>
+      </c>
+      <c r="E157" t="s">
+        <v>250</v>
+      </c>
+      <c r="F157" t="s">
         <v>281</v>
       </c>
-      <c r="C157" t="s">
-        <v>23</v>
-      </c>
-      <c r="D157" t="s">
-        <v>24</v>
-      </c>
-      <c r="E157" t="s">
-        <v>240</v>
-      </c>
-      <c r="F157" t="s">
-        <v>271</v>
-      </c>
       <c r="G157" t="s">
         <v>27</v>
       </c>
@@ -12550,7 +12574,7 @@
         <v>29</v>
       </c>
       <c r="L157" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M157" t="s">
         <v>31</v>
@@ -12588,7 +12612,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C158" t="s">
         <v>23</v>
@@ -12597,10 +12621,10 @@
         <v>24</v>
       </c>
       <c r="E158" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F158" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G158" t="s">
         <v>27</v>
@@ -12618,7 +12642,7 @@
         <v>29</v>
       </c>
       <c r="L158" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M158" t="s">
         <v>31</v>
@@ -12656,7 +12680,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="C159" t="s">
         <v>23</v>
@@ -12665,10 +12689,10 @@
         <v>24</v>
       </c>
       <c r="E159" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F159" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="G159" t="s">
         <v>27</v>
@@ -12686,7 +12710,7 @@
         <v>29</v>
       </c>
       <c r="L159" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M159" t="s">
         <v>31</v>
@@ -12724,7 +12748,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C160" t="s">
         <v>23</v>
@@ -12733,10 +12757,10 @@
         <v>24</v>
       </c>
       <c r="E160" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F160" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="G160" t="s">
         <v>27</v>
@@ -12754,7 +12778,7 @@
         <v>29</v>
       </c>
       <c r="L160" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M160" t="s">
         <v>31</v>
@@ -12792,7 +12816,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="C161" t="s">
         <v>23</v>
@@ -12801,10 +12825,10 @@
         <v>24</v>
       </c>
       <c r="E161" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F161" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="G161" t="s">
         <v>27</v>
@@ -12822,7 +12846,7 @@
         <v>29</v>
       </c>
       <c r="L161" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M161" t="s">
         <v>31</v>
@@ -12860,7 +12884,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C162" t="s">
         <v>23</v>
@@ -12869,10 +12893,10 @@
         <v>24</v>
       </c>
       <c r="E162" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F162" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G162" t="s">
         <v>27</v>
@@ -12890,7 +12914,7 @@
         <v>29</v>
       </c>
       <c r="L162" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M162" t="s">
         <v>31</v>
@@ -12928,7 +12952,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C163" t="s">
         <v>23</v>
@@ -12937,7 +12961,7 @@
         <v>24</v>
       </c>
       <c r="E163" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F163" t="s">
         <v>51</v>
@@ -12958,7 +12982,7 @@
         <v>29</v>
       </c>
       <c r="L163" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M163" t="s">
         <v>31</v>
@@ -12996,7 +13020,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C164" t="s">
         <v>23</v>
@@ -13005,7 +13029,7 @@
         <v>24</v>
       </c>
       <c r="E164" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F164" t="s">
         <v>40</v>
@@ -13026,7 +13050,7 @@
         <v>29</v>
       </c>
       <c r="L164" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M164" t="s">
         <v>31</v>
@@ -13064,7 +13088,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="C165" t="s">
         <v>23</v>
@@ -13073,7 +13097,7 @@
         <v>24</v>
       </c>
       <c r="E165" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F165" t="s">
         <v>40</v>
@@ -13094,7 +13118,7 @@
         <v>29</v>
       </c>
       <c r="L165" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M165" t="s">
         <v>31</v>
@@ -13134,6 +13158,11 @@
     <hyperlink ref="O4" r:id="rId3" display="https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-evropeyskiy"/>
     <hyperlink ref="O6" r:id="rId4" display="https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-konyachnyy"/>
     <hyperlink ref="O5" r:id="rId5" display="https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-zernistyy"/>
+    <hyperlink ref="O7" r:id="rId6" display="https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-olimpiyskiy1"/>
+    <hyperlink ref="O8" r:id="rId7" display="https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-orehovyy"/>
+    <hyperlink ref="O9" r:id="rId8" display="https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-premer"/>
+    <hyperlink ref="O10" r:id="rId9" display="https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-chesnochnyy"/>
+    <hyperlink ref="O11" r:id="rId10" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/doctor-cellofan"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3466" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3465" uniqueCount="321">
   <si>
     <t>id</t>
   </si>
@@ -251,18 +251,36 @@
     <t>0,7-0,8кг в шт.</t>
   </si>
   <si>
+    <t>dokkru.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/doctor-natural-krug</t>
+  </si>
+  <si>
     <t>Докторская Колбаса в н/о ГОСТ</t>
   </si>
   <si>
     <t>1,5-1,8кг в шт.</t>
   </si>
   <si>
+    <t>dokno.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/doctor-naturalnaya-obl</t>
+  </si>
+  <si>
     <t>Докторская Колбаса ГОСТ в б/о 500 гр</t>
   </si>
   <si>
     <t>500гр шт.</t>
   </si>
   <si>
+    <t>dok500.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/doctorskaya500</t>
+  </si>
+  <si>
     <t>Колбаса Докторская "по-Петродворски"</t>
   </si>
   <si>
@@ -275,6 +293,12 @@
     <t>500гр в шт</t>
   </si>
   <si>
+    <t>dokpet.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/doctor-petrodvorski</t>
+  </si>
+  <si>
     <t>Колбаса Ливерная "Славянская" кольцом (Целлофан)</t>
   </si>
   <si>
@@ -287,21 +311,45 @@
     <t>Любительская Колбаса в "Целлофане" ГОСТ</t>
   </si>
   <si>
+    <t>lubcel.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/lyubitelskaya-cellofan</t>
+  </si>
+  <si>
     <t>Любительская Колбаса в н/о ГОСТ</t>
   </si>
   <si>
     <t>1,5-1,7кг в шт.</t>
   </si>
   <si>
+    <t>lubno.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/lyubitelskaya-natural</t>
+  </si>
+  <si>
     <t>Молочная колбаса в б/о ГОСТ</t>
   </si>
   <si>
+    <t>kolmol.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/molochnaya</t>
+  </si>
+  <si>
     <t>Мортаделла Колбаса кусок 0,5</t>
   </si>
   <si>
     <t>0,5-0,6 кг</t>
   </si>
   <si>
+    <t>kolmor.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/mortadella</t>
+  </si>
+  <si>
     <t>Мортаделла Колбаса ПОЛ БАТОНА</t>
   </si>
   <si>
@@ -311,13 +359,28 @@
     <t>Русская Колбаса в "Целлофане" ГОСТ</t>
   </si>
   <si>
+    <t>ruscel.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/russkaya-cellofan</t>
+  </si>
+  <si>
     <t>Русская Колбаса в н/о "Пузырь"</t>
   </si>
   <si>
     <t>Русская Колбаса в н/о ГОСТ</t>
   </si>
   <si>
+    <t>rusno.jpg</t>
+  </si>
+  <si>
     <t>Телячья Колбаса  в н/о ГОСТ</t>
+  </si>
+  <si>
+    <t>koltel.jpg</t>
+  </si>
+  <si>
+    <t>https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/telyachya</t>
   </si>
   <si>
     <t>Чайная Колбаса н/о</t>
@@ -1562,14 +1625,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1929,6 +1994,7 @@
     <col min="9" max="10" width="40" customWidth="1"/>
     <col min="11" max="13" width="18" customWidth="1"/>
     <col min="14" max="14" width="40" customWidth="1"/>
+    <col min="15" max="15" width="35.5263157894737" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -2770,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="I13" t="s">
         <v>29</v>
@@ -2790,8 +2856,8 @@
       <c r="N13" t="s">
         <v>32</v>
       </c>
-      <c r="O13" t="s">
-        <v>29</v>
+      <c r="O13" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="P13" t="s">
         <v>29</v>
@@ -2820,7 +2886,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -2832,13 +2898,13 @@
         <v>65</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s">
         <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="I14" t="s">
         <v>29</v>
@@ -2858,8 +2924,8 @@
       <c r="N14" t="s">
         <v>32</v>
       </c>
-      <c r="O14" t="s">
-        <v>29</v>
+      <c r="O14" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="P14" t="s">
         <v>29</v>
@@ -2888,7 +2954,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -2900,13 +2966,13 @@
         <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s">
         <v>27</v>
       </c>
       <c r="H15" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s">
         <v>29</v>
@@ -2926,8 +2992,8 @@
       <c r="N15" t="s">
         <v>32</v>
       </c>
-      <c r="O15" t="s">
-        <v>29</v>
+      <c r="O15" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="P15" t="s">
         <v>29</v>
@@ -2956,7 +3022,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
@@ -2968,13 +3034,10 @@
         <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s">
         <v>27</v>
-      </c>
-      <c r="H16" t="s">
-        <v>29</v>
       </c>
       <c r="I16" t="s">
         <v>29</v>
@@ -3024,7 +3087,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
@@ -3036,13 +3099,13 @@
         <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s">
         <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s">
         <v>29</v>
@@ -3062,8 +3125,8 @@
       <c r="N17" t="s">
         <v>32</v>
       </c>
-      <c r="O17" t="s">
-        <v>29</v>
+      <c r="O17" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="P17" t="s">
         <v>29</v>
@@ -3092,7 +3155,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -3104,7 +3167,7 @@
         <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s">
         <v>27</v>
@@ -3160,7 +3223,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
         <v>23</v>
@@ -3172,7 +3235,7 @@
         <v>65</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s">
         <v>27</v>
@@ -3228,7 +3291,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -3246,7 +3309,7 @@
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="I20" t="s">
         <v>29</v>
@@ -3266,8 +3329,8 @@
       <c r="N20" t="s">
         <v>32</v>
       </c>
-      <c r="O20" t="s">
-        <v>29</v>
+      <c r="O20" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="P20" t="s">
         <v>29</v>
@@ -3296,7 +3359,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
         <v>23</v>
@@ -3308,13 +3371,13 @@
         <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="I21" t="s">
         <v>29</v>
@@ -3334,8 +3397,8 @@
       <c r="N21" t="s">
         <v>32</v>
       </c>
-      <c r="O21" t="s">
-        <v>29</v>
+      <c r="O21" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="P21" t="s">
         <v>29</v>
@@ -3364,7 +3427,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
@@ -3382,7 +3445,7 @@
         <v>27</v>
       </c>
       <c r="H22" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="I22" t="s">
         <v>29</v>
@@ -3402,8 +3465,8 @@
       <c r="N22" t="s">
         <v>32</v>
       </c>
-      <c r="O22" t="s">
-        <v>29</v>
+      <c r="O22" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="P22" t="s">
         <v>29</v>
@@ -3432,7 +3495,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -3444,13 +3507,13 @@
         <v>65</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
         <v>27</v>
       </c>
       <c r="H23" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="I23" t="s">
         <v>29</v>
@@ -3470,8 +3533,8 @@
       <c r="N23" t="s">
         <v>32</v>
       </c>
-      <c r="O23" t="s">
-        <v>29</v>
+      <c r="O23" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="P23" t="s">
         <v>29</v>
@@ -3500,7 +3563,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
@@ -3512,7 +3575,7 @@
         <v>65</v>
       </c>
       <c r="F24" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="G24" t="s">
         <v>27</v>
@@ -3568,7 +3631,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -3580,13 +3643,13 @@
         <v>65</v>
       </c>
       <c r="F25" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G25" t="s">
         <v>27</v>
       </c>
       <c r="H25" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="I25" t="s">
         <v>29</v>
@@ -3606,8 +3669,8 @@
       <c r="N25" t="s">
         <v>32</v>
       </c>
-      <c r="O25" t="s">
-        <v>29</v>
+      <c r="O25" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="P25" t="s">
         <v>29</v>
@@ -3636,7 +3699,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -3704,7 +3767,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -3716,13 +3779,13 @@
         <v>65</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s">
         <v>27</v>
       </c>
       <c r="H27" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="I27" t="s">
         <v>29</v>
@@ -3742,8 +3805,8 @@
       <c r="N27" t="s">
         <v>32</v>
       </c>
-      <c r="O27" t="s">
-        <v>29</v>
+      <c r="O27" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="P27" t="s">
         <v>29</v>
@@ -3772,7 +3835,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
@@ -3784,13 +3847,13 @@
         <v>65</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="I28" t="s">
         <v>29</v>
@@ -3810,8 +3873,8 @@
       <c r="N28" t="s">
         <v>32</v>
       </c>
-      <c r="O28" t="s">
-        <v>29</v>
+      <c r="O28" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="P28" t="s">
         <v>29</v>
@@ -3840,7 +3903,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -3852,7 +3915,7 @@
         <v>65</v>
       </c>
       <c r="F29" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="G29" t="s">
         <v>27</v>
@@ -3873,7 +3936,7 @@
         <v>68</v>
       </c>
       <c r="M29" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N29" t="s">
         <v>32</v>
@@ -3908,7 +3971,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s">
         <v>23</v>
@@ -3920,7 +3983,7 @@
         <v>65</v>
       </c>
       <c r="F30" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="G30" t="s">
         <v>27</v>
@@ -3976,7 +4039,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -4044,7 +4107,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
         <v>23</v>
@@ -4112,7 +4175,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
         <v>23</v>
@@ -4124,7 +4187,7 @@
         <v>65</v>
       </c>
       <c r="F33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
@@ -4180,7 +4243,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
         <v>23</v>
@@ -4192,7 +4255,7 @@
         <v>65</v>
       </c>
       <c r="F34" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="G34" t="s">
         <v>27</v>
@@ -4248,7 +4311,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
@@ -4260,7 +4323,7 @@
         <v>65</v>
       </c>
       <c r="F35" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
@@ -4316,7 +4379,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
@@ -4328,7 +4391,7 @@
         <v>65</v>
       </c>
       <c r="F36" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="G36" t="s">
         <v>27</v>
@@ -4384,7 +4447,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
@@ -4396,7 +4459,7 @@
         <v>65</v>
       </c>
       <c r="F37" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="G37" t="s">
         <v>27</v>
@@ -4414,10 +4477,10 @@
         <v>29</v>
       </c>
       <c r="L37" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="M37" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="N37" t="s">
         <v>32</v>
@@ -4452,7 +4515,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -4464,7 +4527,7 @@
         <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="G38" t="s">
         <v>27</v>
@@ -4482,7 +4545,7 @@
         <v>29</v>
       </c>
       <c r="L38" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M38" t="s">
         <v>31</v>
@@ -4520,7 +4583,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
         <v>23</v>
@@ -4588,7 +4651,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s">
         <v>23</v>
@@ -4600,7 +4663,7 @@
         <v>65</v>
       </c>
       <c r="F40" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="G40" t="s">
         <v>27</v>
@@ -4656,7 +4719,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
@@ -4668,7 +4731,7 @@
         <v>65</v>
       </c>
       <c r="F41" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="G41" t="s">
         <v>27</v>
@@ -4724,7 +4787,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
         <v>23</v>
@@ -4736,7 +4799,7 @@
         <v>65</v>
       </c>
       <c r="F42" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="G42" t="s">
         <v>27</v>
@@ -4792,7 +4855,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
         <v>23</v>
@@ -4804,7 +4867,7 @@
         <v>65</v>
       </c>
       <c r="F43" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="G43" t="s">
         <v>27</v>
@@ -4860,7 +4923,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C44" t="s">
         <v>23</v>
@@ -4872,7 +4935,7 @@
         <v>65</v>
       </c>
       <c r="F44" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="G44" t="s">
         <v>27</v>
@@ -4890,7 +4953,7 @@
         <v>29</v>
       </c>
       <c r="L44" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M44" t="s">
         <v>31</v>
@@ -4928,7 +4991,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="C45" t="s">
         <v>23</v>
@@ -4940,7 +5003,7 @@
         <v>65</v>
       </c>
       <c r="F45" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="G45" t="s">
         <v>27</v>
@@ -4996,7 +5059,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C46" t="s">
         <v>23</v>
@@ -5008,7 +5071,7 @@
         <v>65</v>
       </c>
       <c r="F46" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="G46" t="s">
         <v>27</v>
@@ -5064,7 +5127,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -5076,7 +5139,7 @@
         <v>65</v>
       </c>
       <c r="F47" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="G47" t="s">
         <v>27</v>
@@ -5132,7 +5195,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
         <v>23</v>
@@ -5144,7 +5207,7 @@
         <v>65</v>
       </c>
       <c r="F48" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="G48" t="s">
         <v>27</v>
@@ -5200,7 +5263,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C49" t="s">
         <v>23</v>
@@ -5212,7 +5275,7 @@
         <v>65</v>
       </c>
       <c r="F49" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="G49" t="s">
         <v>27</v>
@@ -5268,7 +5331,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C50" t="s">
         <v>23</v>
@@ -5336,7 +5399,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s">
         <v>23</v>
@@ -5348,7 +5411,7 @@
         <v>65</v>
       </c>
       <c r="F51" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="G51" t="s">
         <v>27</v>
@@ -5404,7 +5467,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
@@ -5416,7 +5479,7 @@
         <v>65</v>
       </c>
       <c r="F52" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
@@ -5472,7 +5535,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
@@ -5484,7 +5547,7 @@
         <v>65</v>
       </c>
       <c r="F53" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="G53" t="s">
         <v>27</v>
@@ -5540,7 +5603,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
@@ -5552,7 +5615,7 @@
         <v>65</v>
       </c>
       <c r="F54" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="G54" t="s">
         <v>27</v>
@@ -5608,7 +5671,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
@@ -5620,7 +5683,7 @@
         <v>65</v>
       </c>
       <c r="F55" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="G55" t="s">
         <v>27</v>
@@ -5676,7 +5739,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
@@ -5688,7 +5751,7 @@
         <v>65</v>
       </c>
       <c r="F56" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="G56" t="s">
         <v>27</v>
@@ -5744,7 +5807,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="C57" t="s">
         <v>23</v>
@@ -5756,7 +5819,7 @@
         <v>65</v>
       </c>
       <c r="F57" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="G57" t="s">
         <v>27</v>
@@ -5812,7 +5875,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C58" t="s">
         <v>23</v>
@@ -5824,7 +5887,7 @@
         <v>65</v>
       </c>
       <c r="F58" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="G58" t="s">
         <v>27</v>
@@ -5880,7 +5943,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C59" t="s">
         <v>23</v>
@@ -5892,7 +5955,7 @@
         <v>65</v>
       </c>
       <c r="F59" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="G59" t="s">
         <v>27</v>
@@ -5948,7 +6011,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
@@ -5960,7 +6023,7 @@
         <v>65</v>
       </c>
       <c r="F60" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -6016,7 +6079,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -6028,7 +6091,7 @@
         <v>65</v>
       </c>
       <c r="F61" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -6084,7 +6147,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="C62" t="s">
         <v>23</v>
@@ -6096,7 +6159,7 @@
         <v>65</v>
       </c>
       <c r="F62" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -6152,7 +6215,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="C63" t="s">
         <v>23</v>
@@ -6220,7 +6283,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
@@ -6232,7 +6295,7 @@
         <v>65</v>
       </c>
       <c r="F64" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="G64" t="s">
         <v>27</v>
@@ -6288,7 +6351,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C65" t="s">
         <v>23</v>
@@ -6356,7 +6419,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="C66" t="s">
         <v>23</v>
@@ -6368,7 +6431,7 @@
         <v>65</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -6424,7 +6487,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C67" t="s">
         <v>23</v>
@@ -6436,7 +6499,7 @@
         <v>65</v>
       </c>
       <c r="F67" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="G67" t="s">
         <v>27</v>
@@ -6454,7 +6517,7 @@
         <v>29</v>
       </c>
       <c r="L67" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M67" t="s">
         <v>31</v>
@@ -6492,7 +6555,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C68" t="s">
         <v>23</v>
@@ -6504,7 +6567,7 @@
         <v>65</v>
       </c>
       <c r="F68" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="G68" t="s">
         <v>27</v>
@@ -6560,7 +6623,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
@@ -6572,7 +6635,7 @@
         <v>65</v>
       </c>
       <c r="F69" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="G69" t="s">
         <v>27</v>
@@ -6628,7 +6691,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
@@ -6640,7 +6703,7 @@
         <v>65</v>
       </c>
       <c r="F70" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="G70" t="s">
         <v>27</v>
@@ -6658,10 +6721,10 @@
         <v>29</v>
       </c>
       <c r="L70" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M70" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="N70" t="s">
         <v>32</v>
@@ -6696,7 +6759,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
@@ -6726,10 +6789,10 @@
         <v>29</v>
       </c>
       <c r="L71" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M71" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="N71" t="s">
         <v>32</v>
@@ -6764,7 +6827,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="C72" t="s">
         <v>23</v>
@@ -6794,10 +6857,10 @@
         <v>29</v>
       </c>
       <c r="L72" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M72" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="N72" t="s">
         <v>32</v>
@@ -6832,7 +6895,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="C73" t="s">
         <v>23</v>
@@ -6844,7 +6907,7 @@
         <v>65</v>
       </c>
       <c r="F73" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="G73" t="s">
         <v>27</v>
@@ -6900,7 +6963,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C74" t="s">
         <v>23</v>
@@ -6912,7 +6975,7 @@
         <v>65</v>
       </c>
       <c r="F74" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="G74" t="s">
         <v>27</v>
@@ -6930,7 +6993,7 @@
         <v>29</v>
       </c>
       <c r="L74" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="M74" t="s">
         <v>31</v>
@@ -6968,7 +7031,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="C75" t="s">
         <v>23</v>
@@ -6980,7 +7043,7 @@
         <v>65</v>
       </c>
       <c r="F75" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="G75" t="s">
         <v>27</v>
@@ -7036,7 +7099,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -7048,7 +7111,7 @@
         <v>65</v>
       </c>
       <c r="F76" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="G76" t="s">
         <v>27</v>
@@ -7066,7 +7129,7 @@
         <v>29</v>
       </c>
       <c r="L76" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="M76" t="s">
         <v>31</v>
@@ -7104,7 +7167,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="C77" t="s">
         <v>23</v>
@@ -7116,7 +7179,7 @@
         <v>65</v>
       </c>
       <c r="F77" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="G77" t="s">
         <v>27</v>
@@ -7172,7 +7235,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="C78" t="s">
         <v>23</v>
@@ -7184,7 +7247,7 @@
         <v>65</v>
       </c>
       <c r="F78" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="G78" t="s">
         <v>27</v>
@@ -7202,7 +7265,7 @@
         <v>29</v>
       </c>
       <c r="L78" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="M78" t="s">
         <v>31</v>
@@ -7240,7 +7303,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C79" t="s">
         <v>23</v>
@@ -7252,7 +7315,7 @@
         <v>65</v>
       </c>
       <c r="F79" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="G79" t="s">
         <v>27</v>
@@ -7308,7 +7371,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C80" t="s">
         <v>23</v>
@@ -7341,7 +7404,7 @@
         <v>30</v>
       </c>
       <c r="M80" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="N80" t="s">
         <v>32</v>
@@ -7376,7 +7439,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="C81" t="s">
         <v>23</v>
@@ -7409,7 +7472,7 @@
         <v>30</v>
       </c>
       <c r="M81" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="N81" t="s">
         <v>32</v>
@@ -7444,7 +7507,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
@@ -7456,7 +7519,7 @@
         <v>65</v>
       </c>
       <c r="F82" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G82" t="s">
         <v>27</v>
@@ -7477,7 +7540,7 @@
         <v>30</v>
       </c>
       <c r="M82" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="N82" t="s">
         <v>32</v>
@@ -7512,7 +7575,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
@@ -7524,7 +7587,7 @@
         <v>65</v>
       </c>
       <c r="F83" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="G83" t="s">
         <v>27</v>
@@ -7545,7 +7608,7 @@
         <v>30</v>
       </c>
       <c r="M83" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="N83" t="s">
         <v>32</v>
@@ -7580,7 +7643,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="C84" t="s">
         <v>23</v>
@@ -7592,7 +7655,7 @@
         <v>65</v>
       </c>
       <c r="F84" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="G84" t="s">
         <v>27</v>
@@ -7610,10 +7673,10 @@
         <v>29</v>
       </c>
       <c r="L84" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="M84" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="N84" t="s">
         <v>32</v>
@@ -7648,7 +7711,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
@@ -7660,7 +7723,7 @@
         <v>65</v>
       </c>
       <c r="F85" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="G85" t="s">
         <v>27</v>
@@ -7678,10 +7741,10 @@
         <v>29</v>
       </c>
       <c r="L85" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="M85" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="N85" t="s">
         <v>32</v>
@@ -7716,7 +7779,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C86" t="s">
         <v>23</v>
@@ -7728,7 +7791,7 @@
         <v>65</v>
       </c>
       <c r="F86" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="G86" t="s">
         <v>27</v>
@@ -7746,10 +7809,10 @@
         <v>29</v>
       </c>
       <c r="L86" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="M86" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="N86" t="s">
         <v>32</v>
@@ -7784,7 +7847,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
@@ -7817,7 +7880,7 @@
         <v>30</v>
       </c>
       <c r="M87" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="N87" t="s">
         <v>32</v>
@@ -7852,7 +7915,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C88" t="s">
         <v>23</v>
@@ -7864,7 +7927,7 @@
         <v>65</v>
       </c>
       <c r="F88" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="G88" t="s">
         <v>27</v>
@@ -7920,7 +7983,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C89" t="s">
         <v>23</v>
@@ -7929,7 +7992,7 @@
         <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F89" t="s">
         <v>58</v>
@@ -7988,7 +8051,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="C90" t="s">
         <v>23</v>
@@ -7997,10 +8060,10 @@
         <v>24</v>
       </c>
       <c r="E90" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F90" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G90" t="s">
         <v>27</v>
@@ -8021,7 +8084,7 @@
         <v>30</v>
       </c>
       <c r="M90" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N90" t="s">
         <v>32</v>
@@ -8056,7 +8119,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C91" t="s">
         <v>23</v>
@@ -8065,7 +8128,7 @@
         <v>24</v>
       </c>
       <c r="E91" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F91" t="s">
         <v>26</v>
@@ -8124,7 +8187,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="C92" t="s">
         <v>23</v>
@@ -8133,10 +8196,10 @@
         <v>24</v>
       </c>
       <c r="E92" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F92" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G92" t="s">
         <v>27</v>
@@ -8157,7 +8220,7 @@
         <v>30</v>
       </c>
       <c r="M92" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N92" t="s">
         <v>32</v>
@@ -8192,7 +8255,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C93" t="s">
         <v>23</v>
@@ -8201,7 +8264,7 @@
         <v>24</v>
       </c>
       <c r="E93" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F93" t="s">
         <v>58</v>
@@ -8222,10 +8285,10 @@
         <v>29</v>
       </c>
       <c r="L93" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="M93" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="N93" t="s">
         <v>32</v>
@@ -8260,7 +8323,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="C94" t="s">
         <v>23</v>
@@ -8269,7 +8332,7 @@
         <v>24</v>
       </c>
       <c r="E94" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F94" t="s">
         <v>58</v>
@@ -8328,7 +8391,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C95" t="s">
         <v>23</v>
@@ -8337,10 +8400,10 @@
         <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F95" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="G95" t="s">
         <v>27</v>
@@ -8361,7 +8424,7 @@
         <v>68</v>
       </c>
       <c r="M95" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N95" t="s">
         <v>32</v>
@@ -8396,7 +8459,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="C96" t="s">
         <v>23</v>
@@ -8405,10 +8468,10 @@
         <v>24</v>
       </c>
       <c r="E96" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F96" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="G96" t="s">
         <v>27</v>
@@ -8429,7 +8492,7 @@
         <v>30</v>
       </c>
       <c r="M96" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N96" t="s">
         <v>32</v>
@@ -8464,7 +8527,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C97" t="s">
         <v>23</v>
@@ -8473,10 +8536,10 @@
         <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F97" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G97" t="s">
         <v>27</v>
@@ -8497,7 +8560,7 @@
         <v>30</v>
       </c>
       <c r="M97" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N97" t="s">
         <v>32</v>
@@ -8532,7 +8595,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="C98" t="s">
         <v>23</v>
@@ -8541,10 +8604,10 @@
         <v>24</v>
       </c>
       <c r="E98" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F98" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="G98" t="s">
         <v>27</v>
@@ -8565,7 +8628,7 @@
         <v>30</v>
       </c>
       <c r="M98" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N98" t="s">
         <v>32</v>
@@ -8600,7 +8663,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
@@ -8609,7 +8672,7 @@
         <v>24</v>
       </c>
       <c r="E99" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F99" t="s">
         <v>58</v>
@@ -8668,7 +8731,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
@@ -8677,10 +8740,10 @@
         <v>24</v>
       </c>
       <c r="E100" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F100" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G100" t="s">
         <v>27</v>
@@ -8701,7 +8764,7 @@
         <v>30</v>
       </c>
       <c r="M100" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N100" t="s">
         <v>32</v>
@@ -8736,7 +8799,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="C101" t="s">
         <v>23</v>
@@ -8745,10 +8808,10 @@
         <v>24</v>
       </c>
       <c r="E101" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F101" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G101" t="s">
         <v>27</v>
@@ -8769,7 +8832,7 @@
         <v>30</v>
       </c>
       <c r="M101" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N101" t="s">
         <v>32</v>
@@ -8804,7 +8867,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
@@ -8813,10 +8876,10 @@
         <v>24</v>
       </c>
       <c r="E102" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F102" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G102" t="s">
         <v>27</v>
@@ -8837,7 +8900,7 @@
         <v>30</v>
       </c>
       <c r="M102" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N102" t="s">
         <v>32</v>
@@ -8872,7 +8935,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
@@ -8881,10 +8944,10 @@
         <v>24</v>
       </c>
       <c r="E103" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F103" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G103" t="s">
         <v>27</v>
@@ -8905,7 +8968,7 @@
         <v>30</v>
       </c>
       <c r="M103" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N103" t="s">
         <v>32</v>
@@ -8940,7 +9003,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C104" t="s">
         <v>23</v>
@@ -8949,7 +9012,7 @@
         <v>24</v>
       </c>
       <c r="E104" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F104" t="s">
         <v>26</v>
@@ -9008,7 +9071,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
@@ -9017,7 +9080,7 @@
         <v>24</v>
       </c>
       <c r="E105" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F105" t="s">
         <v>40</v>
@@ -9041,7 +9104,7 @@
         <v>30</v>
       </c>
       <c r="M105" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N105" t="s">
         <v>32</v>
@@ -9076,16 +9139,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>241</v>
+      </c>
+      <c r="C106" t="s">
+        <v>23</v>
+      </c>
+      <c r="D106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" t="s">
         <v>220</v>
-      </c>
-      <c r="C106" t="s">
-        <v>23</v>
-      </c>
-      <c r="D106" t="s">
-        <v>24</v>
-      </c>
-      <c r="E106" t="s">
-        <v>199</v>
       </c>
       <c r="F106" t="s">
         <v>73</v>
@@ -9144,7 +9207,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C107" t="s">
         <v>23</v>
@@ -9153,10 +9216,10 @@
         <v>24</v>
       </c>
       <c r="E107" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F107" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G107" t="s">
         <v>27</v>
@@ -9177,7 +9240,7 @@
         <v>30</v>
       </c>
       <c r="M107" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N107" t="s">
         <v>32</v>
@@ -9212,7 +9275,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="C108" t="s">
         <v>23</v>
@@ -9221,10 +9284,10 @@
         <v>24</v>
       </c>
       <c r="E108" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F108" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="G108" t="s">
         <v>27</v>
@@ -9245,7 +9308,7 @@
         <v>30</v>
       </c>
       <c r="M108" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="N108" t="s">
         <v>32</v>
@@ -9280,7 +9343,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="C109" t="s">
         <v>23</v>
@@ -9289,10 +9352,10 @@
         <v>24</v>
       </c>
       <c r="E109" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F109" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="G109" t="s">
         <v>27</v>
@@ -9310,7 +9373,7 @@
         <v>29</v>
       </c>
       <c r="L109" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="M109" t="s">
         <v>31</v>
@@ -9348,7 +9411,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="C110" t="s">
         <v>23</v>
@@ -9357,10 +9420,10 @@
         <v>24</v>
       </c>
       <c r="E110" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F110" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="G110" t="s">
         <v>27</v>
@@ -9378,7 +9441,7 @@
         <v>29</v>
       </c>
       <c r="L110" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="M110" t="s">
         <v>31</v>
@@ -9416,7 +9479,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="C111" t="s">
         <v>23</v>
@@ -9425,10 +9488,10 @@
         <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F111" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="G111" t="s">
         <v>27</v>
@@ -9446,7 +9509,7 @@
         <v>29</v>
       </c>
       <c r="L111" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="M111" t="s">
         <v>31</v>
@@ -9484,7 +9547,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="C112" t="s">
         <v>23</v>
@@ -9493,10 +9556,10 @@
         <v>24</v>
       </c>
       <c r="E112" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F112" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="G112" t="s">
         <v>27</v>
@@ -9514,10 +9577,10 @@
         <v>29</v>
       </c>
       <c r="L112" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="M112" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="N112" t="s">
         <v>32</v>
@@ -9552,7 +9615,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C113" t="s">
         <v>23</v>
@@ -9561,10 +9624,10 @@
         <v>24</v>
       </c>
       <c r="E113" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F113" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -9620,7 +9683,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="C114" t="s">
         <v>23</v>
@@ -9629,10 +9692,10 @@
         <v>24</v>
       </c>
       <c r="E114" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F114" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -9688,7 +9751,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
@@ -9697,10 +9760,10 @@
         <v>24</v>
       </c>
       <c r="E115" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F115" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="G115" t="s">
         <v>27</v>
@@ -9756,7 +9819,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
@@ -9765,10 +9828,10 @@
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F116" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="G116" t="s">
         <v>27</v>
@@ -9824,7 +9887,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="C117" t="s">
         <v>23</v>
@@ -9833,10 +9896,10 @@
         <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F117" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="G117" t="s">
         <v>27</v>
@@ -9892,7 +9955,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="C118" t="s">
         <v>23</v>
@@ -9901,10 +9964,10 @@
         <v>24</v>
       </c>
       <c r="E118" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F118" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="G118" t="s">
         <v>27</v>
@@ -9960,7 +10023,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -9969,10 +10032,10 @@
         <v>24</v>
       </c>
       <c r="E119" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F119" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G119" t="s">
         <v>27</v>
@@ -9993,7 +10056,7 @@
         <v>68</v>
       </c>
       <c r="M119" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N119" t="s">
         <v>32</v>
@@ -10028,7 +10091,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="C120" t="s">
         <v>23</v>
@@ -10037,10 +10100,10 @@
         <v>24</v>
       </c>
       <c r="E120" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F120" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G120" t="s">
         <v>27</v>
@@ -10061,7 +10124,7 @@
         <v>68</v>
       </c>
       <c r="M120" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N120" t="s">
         <v>32</v>
@@ -10096,7 +10159,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C121" t="s">
         <v>23</v>
@@ -10105,10 +10168,10 @@
         <v>24</v>
       </c>
       <c r="E121" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F121" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G121" t="s">
         <v>27</v>
@@ -10129,7 +10192,7 @@
         <v>68</v>
       </c>
       <c r="M121" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N121" t="s">
         <v>32</v>
@@ -10164,7 +10227,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="C122" t="s">
         <v>23</v>
@@ -10173,10 +10236,10 @@
         <v>24</v>
       </c>
       <c r="E122" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F122" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -10197,7 +10260,7 @@
         <v>68</v>
       </c>
       <c r="M122" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N122" t="s">
         <v>32</v>
@@ -10232,7 +10295,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="C123" t="s">
         <v>23</v>
@@ -10241,10 +10304,10 @@
         <v>24</v>
       </c>
       <c r="E123" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F123" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -10265,7 +10328,7 @@
         <v>68</v>
       </c>
       <c r="M123" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N123" t="s">
         <v>32</v>
@@ -10300,7 +10363,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="C124" t="s">
         <v>23</v>
@@ -10309,10 +10372,10 @@
         <v>24</v>
       </c>
       <c r="E124" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F124" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G124" t="s">
         <v>27</v>
@@ -10333,7 +10396,7 @@
         <v>68</v>
       </c>
       <c r="M124" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N124" t="s">
         <v>32</v>
@@ -10368,7 +10431,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="C125" t="s">
         <v>23</v>
@@ -10377,10 +10440,10 @@
         <v>24</v>
       </c>
       <c r="E125" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F125" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G125" t="s">
         <v>27</v>
@@ -10401,7 +10464,7 @@
         <v>68</v>
       </c>
       <c r="M125" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N125" t="s">
         <v>32</v>
@@ -10436,7 +10499,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
@@ -10445,10 +10508,10 @@
         <v>24</v>
       </c>
       <c r="E126" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F126" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G126" t="s">
         <v>27</v>
@@ -10469,7 +10532,7 @@
         <v>68</v>
       </c>
       <c r="M126" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N126" t="s">
         <v>32</v>
@@ -10504,7 +10567,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="C127" t="s">
         <v>23</v>
@@ -10513,10 +10576,10 @@
         <v>24</v>
       </c>
       <c r="E127" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F127" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G127" t="s">
         <v>27</v>
@@ -10537,7 +10600,7 @@
         <v>68</v>
       </c>
       <c r="M127" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N127" t="s">
         <v>32</v>
@@ -10572,7 +10635,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
@@ -10581,10 +10644,10 @@
         <v>24</v>
       </c>
       <c r="E128" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F128" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G128" t="s">
         <v>27</v>
@@ -10605,7 +10668,7 @@
         <v>68</v>
       </c>
       <c r="M128" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N128" t="s">
         <v>32</v>
@@ -10640,7 +10703,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
@@ -10649,10 +10712,10 @@
         <v>24</v>
       </c>
       <c r="E129" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F129" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
@@ -10670,7 +10733,7 @@
         <v>29</v>
       </c>
       <c r="L129" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="M129" t="s">
         <v>31</v>
@@ -10708,7 +10771,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
@@ -10717,10 +10780,10 @@
         <v>24</v>
       </c>
       <c r="E130" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F130" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G130" t="s">
         <v>27</v>
@@ -10738,7 +10801,7 @@
         <v>29</v>
       </c>
       <c r="L130" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="M130" t="s">
         <v>31</v>
@@ -10776,7 +10839,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="C131" t="s">
         <v>23</v>
@@ -10785,10 +10848,10 @@
         <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F131" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="G131" t="s">
         <v>27</v>
@@ -10806,7 +10869,7 @@
         <v>29</v>
       </c>
       <c r="L131" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M131" t="s">
         <v>31</v>
@@ -10844,7 +10907,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="C132" t="s">
         <v>23</v>
@@ -10853,10 +10916,10 @@
         <v>24</v>
       </c>
       <c r="E132" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F132" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -10874,7 +10937,7 @@
         <v>29</v>
       </c>
       <c r="L132" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M132" t="s">
         <v>31</v>
@@ -10912,7 +10975,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -10921,10 +10984,10 @@
         <v>24</v>
       </c>
       <c r="E133" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F133" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="G133" t="s">
         <v>27</v>
@@ -10942,7 +11005,7 @@
         <v>29</v>
       </c>
       <c r="L133" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="M133" t="s">
         <v>31</v>
@@ -10980,7 +11043,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="C134" t="s">
         <v>23</v>
@@ -10989,10 +11052,10 @@
         <v>24</v>
       </c>
       <c r="E134" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F134" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="G134" t="s">
         <v>27</v>
@@ -11010,7 +11073,7 @@
         <v>29</v>
       </c>
       <c r="L134" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M134" t="s">
         <v>31</v>
@@ -11048,7 +11111,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="C135" t="s">
         <v>23</v>
@@ -11057,10 +11120,10 @@
         <v>24</v>
       </c>
       <c r="E135" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F135" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="G135" t="s">
         <v>27</v>
@@ -11078,7 +11141,7 @@
         <v>29</v>
       </c>
       <c r="L135" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="M135" t="s">
         <v>31</v>
@@ -11116,7 +11179,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="C136" t="s">
         <v>23</v>
@@ -11125,10 +11188,10 @@
         <v>24</v>
       </c>
       <c r="E136" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F136" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="G136" t="s">
         <v>27</v>
@@ -11146,10 +11209,10 @@
         <v>29</v>
       </c>
       <c r="L136" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="M136" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="N136" t="s">
         <v>32</v>
@@ -11184,7 +11247,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="C137" t="s">
         <v>23</v>
@@ -11193,10 +11256,10 @@
         <v>24</v>
       </c>
       <c r="E137" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F137" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G137" t="s">
         <v>27</v>
@@ -11214,7 +11277,7 @@
         <v>29</v>
       </c>
       <c r="L137" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="M137" t="s">
         <v>31</v>
@@ -11252,7 +11315,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="C138" t="s">
         <v>23</v>
@@ -11261,10 +11324,10 @@
         <v>24</v>
       </c>
       <c r="E138" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F138" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G138" t="s">
         <v>27</v>
@@ -11282,7 +11345,7 @@
         <v>29</v>
       </c>
       <c r="L138" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="M138" t="s">
         <v>31</v>
@@ -11320,7 +11383,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="C139" t="s">
         <v>23</v>
@@ -11329,10 +11392,10 @@
         <v>24</v>
       </c>
       <c r="E139" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F139" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="G139" t="s">
         <v>27</v>
@@ -11388,7 +11451,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="C140" t="s">
         <v>23</v>
@@ -11397,10 +11460,10 @@
         <v>24</v>
       </c>
       <c r="E140" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F140" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="G140" t="s">
         <v>27</v>
@@ -11456,7 +11519,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="C141" t="s">
         <v>23</v>
@@ -11465,10 +11528,10 @@
         <v>24</v>
       </c>
       <c r="E141" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="G141" t="s">
         <v>27</v>
@@ -11524,7 +11587,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="C142" t="s">
         <v>23</v>
@@ -11533,10 +11596,10 @@
         <v>24</v>
       </c>
       <c r="E142" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="G142" t="s">
         <v>27</v>
@@ -11592,19 +11655,19 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
+        <v>292</v>
+      </c>
+      <c r="C143" t="s">
+        <v>23</v>
+      </c>
+      <c r="D143" t="s">
+        <v>24</v>
+      </c>
+      <c r="E143" t="s">
         <v>271</v>
       </c>
-      <c r="C143" t="s">
-        <v>23</v>
-      </c>
-      <c r="D143" t="s">
-        <v>24</v>
-      </c>
-      <c r="E143" t="s">
-        <v>250</v>
-      </c>
       <c r="F143" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="G143" t="s">
         <v>27</v>
@@ -11660,7 +11723,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="C144" t="s">
         <v>23</v>
@@ -11669,10 +11732,10 @@
         <v>24</v>
       </c>
       <c r="E144" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F144" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="G144" t="s">
         <v>27</v>
@@ -11728,7 +11791,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="C145" t="s">
         <v>23</v>
@@ -11737,10 +11800,10 @@
         <v>24</v>
       </c>
       <c r="E145" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F145" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="G145" t="s">
         <v>27</v>
@@ -11796,7 +11859,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="C146" t="s">
         <v>23</v>
@@ -11805,10 +11868,10 @@
         <v>24</v>
       </c>
       <c r="E146" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="G146" t="s">
         <v>27</v>
@@ -11864,7 +11927,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C147" t="s">
         <v>23</v>
@@ -11873,10 +11936,10 @@
         <v>24</v>
       </c>
       <c r="E147" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="G147" t="s">
         <v>27</v>
@@ -11932,7 +11995,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C148" t="s">
         <v>23</v>
@@ -11941,10 +12004,10 @@
         <v>24</v>
       </c>
       <c r="E148" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="G148" t="s">
         <v>27</v>
@@ -12000,7 +12063,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="C149" t="s">
         <v>23</v>
@@ -12009,10 +12072,10 @@
         <v>24</v>
       </c>
       <c r="E149" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="G149" t="s">
         <v>27</v>
@@ -12068,7 +12131,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="C150" t="s">
         <v>23</v>
@@ -12077,10 +12140,10 @@
         <v>24</v>
       </c>
       <c r="E150" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="G150" t="s">
         <v>27</v>
@@ -12136,7 +12199,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="C151" t="s">
         <v>23</v>
@@ -12145,10 +12208,10 @@
         <v>24</v>
       </c>
       <c r="E151" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="G151" t="s">
         <v>27</v>
@@ -12204,7 +12267,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="C152" t="s">
         <v>23</v>
@@ -12213,10 +12276,10 @@
         <v>24</v>
       </c>
       <c r="E152" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="G152" t="s">
         <v>27</v>
@@ -12272,7 +12335,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="C153" t="s">
         <v>23</v>
@@ -12281,10 +12344,10 @@
         <v>24</v>
       </c>
       <c r="E153" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G153" t="s">
         <v>27</v>
@@ -12340,7 +12403,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="C154" t="s">
         <v>23</v>
@@ -12349,10 +12412,10 @@
         <v>24</v>
       </c>
       <c r="E154" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="G154" t="s">
         <v>27</v>
@@ -12408,7 +12471,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C155" t="s">
         <v>23</v>
@@ -12417,10 +12480,10 @@
         <v>24</v>
       </c>
       <c r="E155" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="G155" t="s">
         <v>27</v>
@@ -12476,7 +12539,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="C156" t="s">
         <v>23</v>
@@ -12485,10 +12548,10 @@
         <v>24</v>
       </c>
       <c r="E156" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="G156" t="s">
         <v>27</v>
@@ -12544,7 +12607,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C157" t="s">
         <v>23</v>
@@ -12553,10 +12616,10 @@
         <v>24</v>
       </c>
       <c r="E157" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F157" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="G157" t="s">
         <v>27</v>
@@ -12612,7 +12675,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="C158" t="s">
         <v>23</v>
@@ -12621,10 +12684,10 @@
         <v>24</v>
       </c>
       <c r="E158" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="G158" t="s">
         <v>27</v>
@@ -12680,7 +12743,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="C159" t="s">
         <v>23</v>
@@ -12689,10 +12752,10 @@
         <v>24</v>
       </c>
       <c r="E159" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="G159" t="s">
         <v>27</v>
@@ -12748,7 +12811,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C160" t="s">
         <v>23</v>
@@ -12757,10 +12820,10 @@
         <v>24</v>
       </c>
       <c r="E160" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="G160" t="s">
         <v>27</v>
@@ -12816,7 +12879,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="C161" t="s">
         <v>23</v>
@@ -12825,10 +12888,10 @@
         <v>24</v>
       </c>
       <c r="E161" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="G161" t="s">
         <v>27</v>
@@ -12884,7 +12947,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="C162" t="s">
         <v>23</v>
@@ -12893,10 +12956,10 @@
         <v>24</v>
       </c>
       <c r="E162" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="G162" t="s">
         <v>27</v>
@@ -12952,7 +13015,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="C163" t="s">
         <v>23</v>
@@ -12961,7 +13024,7 @@
         <v>24</v>
       </c>
       <c r="E163" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F163" t="s">
         <v>51</v>
@@ -13020,7 +13083,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="C164" t="s">
         <v>23</v>
@@ -13029,7 +13092,7 @@
         <v>24</v>
       </c>
       <c r="E164" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
         <v>40</v>
@@ -13088,7 +13151,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C165" t="s">
         <v>23</v>
@@ -13097,7 +13160,7 @@
         <v>24</v>
       </c>
       <c r="E165" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F165" t="s">
         <v>40</v>
@@ -13163,6 +13226,17 @@
     <hyperlink ref="O9" r:id="rId8" display="https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-premer"/>
     <hyperlink ref="O10" r:id="rId9" display="https://petrovproduct.ru/products/meats/pik/var-kopchenie/servelat-chesnochnyy"/>
     <hyperlink ref="O11" r:id="rId10" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/doctor-cellofan"/>
+    <hyperlink ref="O13" r:id="rId11" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/doctor-natural-krug"/>
+    <hyperlink ref="O14" r:id="rId12" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/doctor-naturalnaya-obl"/>
+    <hyperlink ref="O15" r:id="rId13" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/doctorskaya500"/>
+    <hyperlink ref="O17" r:id="rId14" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/doctor-petrodvorski"/>
+    <hyperlink ref="O20" r:id="rId15" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/lyubitelskaya-cellofan"/>
+    <hyperlink ref="O21" r:id="rId16" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/lyubitelskaya-natural"/>
+    <hyperlink ref="O22" r:id="rId17" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/molochnaya"/>
+    <hyperlink ref="O23" r:id="rId18" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/mortadella"/>
+    <hyperlink ref="O25" r:id="rId19" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/russkaya-cellofan"/>
+    <hyperlink ref="O27" r:id="rId19" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/russkaya-cellofan"/>
+    <hyperlink ref="O28" r:id="rId20" display="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/telyachya" tooltip="https://petrovproduct.ru/products/meats/pik/varenie-kolbasy/telyachya"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -2795,7 +2795,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2804,7 +2804,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -5583,7 +5582,7 @@
       <c r="N36" t="s">
         <v>33</v>
       </c>
-      <c r="O36" s="5" t="s">
+      <c r="O36" s="4" t="s">
         <v>147</v>
       </c>
       <c r="P36" t="s">
@@ -5651,7 +5650,7 @@
       <c r="N37" t="s">
         <v>33</v>
       </c>
-      <c r="O37" s="5" t="s">
+      <c r="O37" s="4" t="s">
         <v>147</v>
       </c>
       <c r="P37" t="s">
@@ -5787,7 +5786,7 @@
       <c r="N39" t="s">
         <v>33</v>
       </c>
-      <c r="O39" s="5" t="s">
+      <c r="O39" s="4" t="s">
         <v>158</v>
       </c>
       <c r="P39" t="s">
@@ -5855,7 +5854,7 @@
       <c r="N40" t="s">
         <v>33</v>
       </c>
-      <c r="O40" s="6" t="s">
+      <c r="O40" s="5" t="s">
         <v>163</v>
       </c>
       <c r="P40" t="s">
@@ -5923,7 +5922,7 @@
       <c r="N41" t="s">
         <v>33</v>
       </c>
-      <c r="O41" s="6" t="s">
+      <c r="O41" s="5" t="s">
         <v>168</v>
       </c>
       <c r="P41" t="s">
@@ -5962,7 +5961,7 @@
         <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="F42" t="s">
         <v>165</v>
@@ -5991,7 +5990,7 @@
       <c r="N42" t="s">
         <v>33</v>
       </c>
-      <c r="O42" s="6" t="s">
+      <c r="O42" s="5" t="s">
         <v>172</v>
       </c>
       <c r="P42" t="s">
@@ -6059,7 +6058,6 @@
       <c r="N43" t="s">
         <v>33</v>
       </c>
-      <c r="O43"/>
       <c r="P43" t="s">
         <v>29</v>
       </c>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -2840,7 +2840,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2849,7 +2849,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -6104,7 +6103,7 @@
       <c r="N43" t="s">
         <v>33</v>
       </c>
-      <c r="O43" s="5" t="s">
+      <c r="O43" s="4" t="s">
         <v>176</v>
       </c>
       <c r="P43" t="s">
@@ -6237,7 +6236,7 @@
       <c r="N45" t="s">
         <v>33</v>
       </c>
-      <c r="O45" s="5" t="s">
+      <c r="O45" s="4" t="s">
         <v>182</v>
       </c>
       <c r="P45" t="s">
@@ -6305,7 +6304,7 @@
       <c r="N46" t="s">
         <v>33</v>
       </c>
-      <c r="O46" s="5" t="s">
+      <c r="O46" s="4" t="s">
         <v>186</v>
       </c>
       <c r="P46" t="s">
@@ -6506,7 +6505,7 @@
       <c r="N49" t="s">
         <v>33</v>
       </c>
-      <c r="O49" s="6" t="s">
+      <c r="O49" s="5" t="s">
         <v>197</v>
       </c>
       <c r="P49" t="s">
@@ -6817,7 +6816,7 @@
         <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="F54" t="s">
         <v>213</v>
@@ -6846,7 +6845,7 @@
       <c r="N54" t="s">
         <v>33</v>
       </c>
-      <c r="O54" s="6" t="s">
+      <c r="O54" s="5" t="s">
         <v>216</v>
       </c>
       <c r="P54" t="s">

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19392" windowHeight="8562"/>
+    <workbookView windowWidth="18954" windowHeight="9162"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -1046,7 +1046,7 @@
     <t>HIT</t>
   </si>
   <si>
-    <t>13,20</t>
+    <t>13|20</t>
   </si>
   <si>
     <t>Колбаски п/к "Домашние" в н/о</t>
@@ -5809,7 +5809,6 @@
       <c r="H35" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
         <v>31</v>
       </c>
@@ -5876,7 +5875,6 @@
       <c r="H36" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
         <v>31</v>
       </c>
@@ -5943,7 +5941,6 @@
       <c r="H37" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
         <v>31</v>
       </c>
@@ -6010,7 +6007,6 @@
       <c r="H38" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
         <v>31</v>
       </c>
@@ -6077,7 +6073,6 @@
       <c r="H39" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I39" s="1"/>
       <c r="J39" s="1" t="s">
         <v>31</v>
       </c>
@@ -6144,7 +6139,6 @@
       <c r="H40" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="I40" s="1"/>
       <c r="J40" s="1" t="s">
         <v>31</v>
       </c>
@@ -6211,7 +6205,6 @@
       <c r="H41" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="I41" s="1"/>
       <c r="J41" s="1" t="s">
         <v>31</v>
       </c>
@@ -6278,7 +6271,6 @@
       <c r="H42" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I42" s="1"/>
       <c r="J42" s="1" t="s">
         <v>31</v>
       </c>
@@ -6345,7 +6337,6 @@
       <c r="H43" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="I43" s="1"/>
       <c r="J43" s="1" t="s">
         <v>31</v>
       </c>
@@ -6412,7 +6403,6 @@
       <c r="H44" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="I44" s="1"/>
       <c r="J44" s="1" t="s">
         <v>31</v>
       </c>
@@ -6479,7 +6469,6 @@
       <c r="H45" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="I45" s="1"/>
       <c r="J45" s="1" t="s">
         <v>31</v>
       </c>
@@ -6546,7 +6535,6 @@
       <c r="H46" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I46" s="1"/>
       <c r="J46" s="1" t="s">
         <v>31</v>
       </c>
@@ -6613,7 +6601,6 @@
       <c r="H47" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I47" s="1"/>
       <c r="J47" s="1" t="s">
         <v>31</v>
       </c>
@@ -6680,7 +6667,6 @@
       <c r="H48" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="I48" s="1"/>
       <c r="J48" s="1" t="s">
         <v>31</v>
       </c>
@@ -6747,7 +6733,6 @@
       <c r="H49" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="I49" s="1"/>
       <c r="J49" s="1" t="s">
         <v>31</v>
       </c>
@@ -6814,7 +6799,6 @@
       <c r="H50" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="I50" s="1"/>
       <c r="J50" s="1" t="s">
         <v>31</v>
       </c>
@@ -6881,7 +6865,6 @@
       <c r="H51" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="I51" s="1"/>
       <c r="J51" s="1" t="s">
         <v>31</v>
       </c>
@@ -6948,7 +6931,6 @@
       <c r="H52" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="I52" s="1"/>
       <c r="J52" s="1" t="s">
         <v>31</v>
       </c>
@@ -7015,7 +6997,6 @@
       <c r="H53" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="I53" s="1"/>
       <c r="J53" s="1" t="s">
         <v>31</v>
       </c>
@@ -7082,7 +7063,6 @@
       <c r="H54" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="I54" s="1"/>
       <c r="J54" s="1" t="s">
         <v>31</v>
       </c>
@@ -7149,7 +7129,6 @@
       <c r="H55" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="I55" s="1"/>
       <c r="J55" s="1" t="s">
         <v>31</v>
       </c>
@@ -7216,7 +7195,6 @@
       <c r="H56" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="I56" s="1"/>
       <c r="J56" s="1" t="s">
         <v>31</v>
       </c>
@@ -7283,7 +7261,6 @@
       <c r="H57" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="I57" s="1"/>
       <c r="J57" s="1" t="s">
         <v>31</v>
       </c>
@@ -7350,7 +7327,6 @@
       <c r="H58" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="I58" s="1"/>
       <c r="J58" s="1" t="s">
         <v>31</v>
       </c>
@@ -7417,7 +7393,6 @@
       <c r="H59" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="I59" s="1"/>
       <c r="J59" s="1" t="s">
         <v>31</v>
       </c>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -3077,28 +3077,28 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="6" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -1586,7 +1586,7 @@
     <t>3 мес</t>
   </si>
   <si>
-    <t>284|343</t>
+    <t>283|342</t>
   </si>
   <si>
     <t>«Мраморный» 45%</t>
@@ -2009,7 +2009,7 @@
     <t>Сыр Моцарелла Пицца ТМ АНТОН ПАЛЫЧ 40%</t>
   </si>
   <si>
-    <t>181|343</t>
+    <t>180|342</t>
   </si>
   <si>
     <t>Сыр "Храброе Сердце" 45% НОВИНКА ТМ Антон Палыч</t>
@@ -2216,7 +2216,7 @@
     <t>Bonfesto</t>
   </si>
   <si>
-    <t>181|284</t>
+    <t>180|283</t>
   </si>
   <si>
     <t>Сыр "ПЕСТО ГРИН" с базиликом и чесноком, 45%"Новогрудские дары"</t>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6029" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6030" uniqueCount="808">
   <si>
     <t>id</t>
   </si>
@@ -2214,6 +2214,9 @@
   </si>
   <si>
     <t>Bonfesto</t>
+  </si>
+  <si>
+    <t>2|3</t>
   </si>
   <si>
     <t>180|283</t>
@@ -21265,8 +21268,11 @@
       <c r="L343" s="12" t="s">
         <v>532</v>
       </c>
+      <c r="Y343" t="s">
+        <v>729</v>
+      </c>
       <c r="Z343" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="344" spans="1:26">
@@ -21274,7 +21280,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="12" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C344" s="12"/>
       <c r="D344" s="12" t="s">
@@ -21308,7 +21314,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C345" s="12"/>
       <c r="D345" s="12" t="s">
@@ -21342,7 +21348,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="12" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C346" s="12" t="s">
         <v>728</v>
@@ -21380,7 +21386,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="12" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C347" s="12" t="s">
         <v>728</v>
@@ -21418,7 +21424,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="12" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C348" s="12" t="s">
         <v>728</v>
@@ -21456,7 +21462,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="12" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C349" s="12" t="s">
         <v>728</v>
@@ -21494,7 +21500,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C350" s="12" t="s">
         <v>728</v>
@@ -21532,7 +21538,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="12" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C351" s="12" t="s">
         <v>728</v>
@@ -21570,7 +21576,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="12" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C352" s="12" t="s">
         <v>728</v>
@@ -21608,7 +21614,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="12" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C353" s="12" t="s">
         <v>728</v>
@@ -21644,10 +21650,10 @@
         <v>353</v>
       </c>
       <c r="B354" s="12" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C354" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D354" s="12" t="s">
         <v>499</v>
@@ -21682,10 +21688,10 @@
         <v>354</v>
       </c>
       <c r="B355" s="12" t="s">
+        <v>743</v>
+      </c>
+      <c r="C355" s="12" t="s">
         <v>742</v>
-      </c>
-      <c r="C355" s="12" t="s">
-        <v>741</v>
       </c>
       <c r="D355" s="12" t="s">
         <v>499</v>
@@ -21720,10 +21726,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="12" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C356" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D356" s="12" t="s">
         <v>499</v>
@@ -21758,10 +21764,10 @@
         <v>356</v>
       </c>
       <c r="B357" s="12" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C357" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D357" s="12" t="s">
         <v>499</v>
@@ -21796,10 +21802,10 @@
         <v>357</v>
       </c>
       <c r="B358" s="12" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C358" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D358" s="12" t="s">
         <v>499</v>
@@ -21834,10 +21840,10 @@
         <v>358</v>
       </c>
       <c r="B359" s="12" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C359" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D359" s="12" t="s">
         <v>499</v>
@@ -21872,10 +21878,10 @@
         <v>359</v>
       </c>
       <c r="B360" s="12" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C360" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D360" s="12" t="s">
         <v>499</v>
@@ -21910,10 +21916,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="12" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C361" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D361" s="12" t="s">
         <v>499</v>
@@ -21948,10 +21954,10 @@
         <v>361</v>
       </c>
       <c r="B362" s="12" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C362" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D362" s="12" t="s">
         <v>499</v>
@@ -21986,10 +21992,10 @@
         <v>362</v>
       </c>
       <c r="B363" s="12" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C363" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D363" s="12" t="s">
         <v>499</v>
@@ -22024,10 +22030,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="12" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C364" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D364" s="12" t="s">
         <v>499</v>
@@ -22062,10 +22068,10 @@
         <v>364</v>
       </c>
       <c r="B365" s="12" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C365" s="12" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D365" s="12" t="s">
         <v>499</v>
@@ -22100,10 +22106,10 @@
         <v>365</v>
       </c>
       <c r="B366" s="12" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C366" s="12" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D366" s="12" t="s">
         <v>499</v>
@@ -22138,10 +22144,10 @@
         <v>366</v>
       </c>
       <c r="B367" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="C367" s="12" t="s">
         <v>756</v>
-      </c>
-      <c r="C367" s="12" t="s">
-        <v>755</v>
       </c>
       <c r="D367" s="12" t="s">
         <v>499</v>
@@ -22176,16 +22182,16 @@
         <v>367</v>
       </c>
       <c r="B368" s="12" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C368" s="12" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D368" s="12" t="s">
         <v>538</v>
       </c>
       <c r="E368" s="12" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F368" s="12" t="s">
         <v>33</v>
@@ -22206,7 +22212,7 @@
         <v>34</v>
       </c>
       <c r="L368" s="12" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="369" spans="1:12">
@@ -22214,16 +22220,16 @@
         <v>368</v>
       </c>
       <c r="B369" s="12" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C369" s="12" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D369" s="12" t="s">
         <v>538</v>
       </c>
       <c r="E369" s="12" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F369" s="12" t="s">
         <v>33</v>
@@ -22244,7 +22250,7 @@
         <v>34</v>
       </c>
       <c r="L369" s="12" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="370" spans="1:12">
@@ -22252,16 +22258,16 @@
         <v>369</v>
       </c>
       <c r="B370" s="12" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C370" s="12" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D370" s="12" t="s">
         <v>538</v>
       </c>
       <c r="E370" s="12" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F370" s="12" t="s">
         <v>33</v>
@@ -22282,7 +22288,7 @@
         <v>34</v>
       </c>
       <c r="L370" s="12" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="371" spans="1:12">
@@ -22290,7 +22296,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="12" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C371" s="12" t="s">
         <v>670</v>
@@ -22326,7 +22332,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="12" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C372" s="12" t="s">
         <v>670</v>
@@ -22354,7 +22360,7 @@
         <v>34</v>
       </c>
       <c r="L372" s="12" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="373" spans="1:12">
@@ -22362,7 +22368,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="12" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C373" s="12" t="s">
         <v>670</v>
@@ -22398,7 +22404,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="12" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C374" s="12" t="s">
         <v>670</v>
@@ -22434,7 +22440,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="12" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C375" s="12" t="s">
         <v>670</v>
@@ -22470,7 +22476,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="12" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C376" s="12" t="s">
         <v>670</v>
@@ -22506,7 +22512,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="12" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C377" s="12" t="s">
         <v>670</v>
@@ -22542,7 +22548,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="12" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C378" s="12" t="s">
         <v>670</v>
@@ -22578,7 +22584,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="12" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C379" s="12" t="s">
         <v>670</v>
@@ -22614,10 +22620,10 @@
         <v>379</v>
       </c>
       <c r="B380" s="12" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C380" s="12" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D380" s="12" t="s">
         <v>499</v>
@@ -22650,10 +22656,10 @@
         <v>380</v>
       </c>
       <c r="B381" s="12" t="s">
+        <v>777</v>
+      </c>
+      <c r="C381" s="12" t="s">
         <v>776</v>
-      </c>
-      <c r="C381" s="12" t="s">
-        <v>775</v>
       </c>
       <c r="D381" s="12" t="s">
         <v>499</v>
@@ -22686,10 +22692,10 @@
         <v>381</v>
       </c>
       <c r="B382" s="12" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C382" s="12" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D382" s="12" t="s">
         <v>499</v>
@@ -22722,10 +22728,10 @@
         <v>382</v>
       </c>
       <c r="B383" s="12" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C383" s="12" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D383" s="12" t="s">
         <v>499</v>
@@ -22758,10 +22764,10 @@
         <v>383</v>
       </c>
       <c r="B384" s="12" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C384" s="12" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D384" s="12" t="s">
         <v>499</v>
@@ -22794,10 +22800,10 @@
         <v>384</v>
       </c>
       <c r="B385" s="12" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C385" s="12" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D385" s="12" t="s">
         <v>499</v>
@@ -22830,10 +22836,10 @@
         <v>385</v>
       </c>
       <c r="B386" s="12" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C386" s="12" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D386" s="12" t="s">
         <v>499</v>
@@ -22866,10 +22872,10 @@
         <v>386</v>
       </c>
       <c r="B387" s="12" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C387" s="12" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D387" s="12" t="s">
         <v>499</v>
@@ -22902,10 +22908,10 @@
         <v>387</v>
       </c>
       <c r="B388" s="12" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C388" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D388" s="12" t="s">
         <v>499</v>
@@ -22940,10 +22946,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="12" t="s">
+        <v>786</v>
+      </c>
+      <c r="C389" s="12" t="s">
         <v>785</v>
-      </c>
-      <c r="C389" s="12" t="s">
-        <v>784</v>
       </c>
       <c r="D389" s="12" t="s">
         <v>499</v>
@@ -22978,10 +22984,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="12" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C390" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D390" s="12" t="s">
         <v>499</v>
@@ -23016,10 +23022,10 @@
         <v>390</v>
       </c>
       <c r="B391" s="12" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C391" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D391" s="12" t="s">
         <v>499</v>
@@ -23054,10 +23060,10 @@
         <v>391</v>
       </c>
       <c r="B392" s="12" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C392" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D392" s="12" t="s">
         <v>499</v>
@@ -23092,10 +23098,10 @@
         <v>392</v>
       </c>
       <c r="B393" s="12" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C393" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D393" s="12" t="s">
         <v>499</v>
@@ -23130,10 +23136,10 @@
         <v>393</v>
       </c>
       <c r="B394" s="12" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C394" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D394" s="12" t="s">
         <v>499</v>
@@ -23168,10 +23174,10 @@
         <v>394</v>
       </c>
       <c r="B395" s="12" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C395" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D395" s="12" t="s">
         <v>499</v>
@@ -23206,10 +23212,10 @@
         <v>395</v>
       </c>
       <c r="B396" s="12" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C396" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D396" s="12" t="s">
         <v>499</v>
@@ -23244,10 +23250,10 @@
         <v>396</v>
       </c>
       <c r="B397" s="12" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C397" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D397" s="12" t="s">
         <v>499</v>
@@ -23282,10 +23288,10 @@
         <v>397</v>
       </c>
       <c r="B398" s="12" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C398" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D398" s="12" t="s">
         <v>499</v>
@@ -23320,10 +23326,10 @@
         <v>398</v>
       </c>
       <c r="B399" s="12" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C399" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D399" s="12" t="s">
         <v>499</v>
@@ -23358,10 +23364,10 @@
         <v>399</v>
       </c>
       <c r="B400" s="12" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C400" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D400" s="12" t="s">
         <v>499</v>
@@ -23396,10 +23402,10 @@
         <v>400</v>
       </c>
       <c r="B401" s="12" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C401" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D401" s="12" t="s">
         <v>499</v>
@@ -23434,10 +23440,10 @@
         <v>401</v>
       </c>
       <c r="B402" s="12" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C402" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D402" s="12" t="s">
         <v>499</v>
@@ -23472,10 +23478,10 @@
         <v>402</v>
       </c>
       <c r="B403" s="12" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C403" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D403" s="12" t="s">
         <v>499</v>
@@ -23510,10 +23516,10 @@
         <v>403</v>
       </c>
       <c r="B404" s="12" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C404" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D404" s="12" t="s">
         <v>499</v>
@@ -23548,10 +23554,10 @@
         <v>404</v>
       </c>
       <c r="B405" s="12" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C405" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D405" s="12" t="s">
         <v>499</v>
@@ -23586,10 +23592,10 @@
         <v>405</v>
       </c>
       <c r="B406" s="12" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C406" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D406" s="12" t="s">
         <v>499</v>
@@ -23624,10 +23630,10 @@
         <v>406</v>
       </c>
       <c r="B407" s="12" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C407" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D407" s="12" t="s">
         <v>499</v>
@@ -23662,10 +23668,10 @@
         <v>407</v>
       </c>
       <c r="B408" s="12" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C408" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D408" s="12" t="s">
         <v>499</v>
@@ -23700,10 +23706,10 @@
         <v>408</v>
       </c>
       <c r="B409" s="12" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C409" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D409" s="12" t="s">
         <v>499</v>
@@ -23738,10 +23744,10 @@
         <v>409</v>
       </c>
       <c r="B410" s="12" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C410" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D410" s="12" t="s">
         <v>499</v>
@@ -23776,10 +23782,10 @@
         <v>410</v>
       </c>
       <c r="B411" s="12" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C411" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D411" s="12" t="s">
         <v>499</v>
@@ -23814,10 +23820,10 @@
         <v>411</v>
       </c>
       <c r="B412" s="12" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C412" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D412" s="12" t="s">
         <v>538</v>
@@ -23842,7 +23848,7 @@
       </c>
       <c r="K412" s="12"/>
       <c r="L412" s="12" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="413" spans="1:12">
@@ -23850,10 +23856,10 @@
         <v>412</v>
       </c>
       <c r="B413" s="12" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C413" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D413" s="12" t="s">
         <v>538</v>
@@ -23878,7 +23884,7 @@
       </c>
       <c r="K413" s="12"/>
       <c r="L413" s="12" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="414" spans="1:12">
@@ -23886,10 +23892,10 @@
         <v>413</v>
       </c>
       <c r="B414" s="12" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C414" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D414" s="12" t="s">
         <v>538</v>
@@ -23914,7 +23920,7 @@
       </c>
       <c r="K414" s="12"/>
       <c r="L414" s="12" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>

--- a/storage/products.xlsx
+++ b/storage/products.xlsx
@@ -21268,7 +21268,7 @@
       <c r="L343" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="Y343" t="s">
+      <c r="X343" t="s">
         <v>729</v>
       </c>
       <c r="Z343" t="s">
